--- a/InputData/trans/SYVbT/Start Year Vehicles by Technology.xlsx
+++ b/InputData/trans/SYVbT/Start Year Vehicles by Technology.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\ND\trans\SYVbT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FF1E572-44FB-4BD3-9FC3-7B7B042B83AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3376DE8-5B8A-46D7-AE7B-CDD5771590C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,12 +63,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="555">
   <si>
     <t>State Vehicles 2024 — SSYVbT Baseline Workbook</t>
   </si>
   <si>
-    <t>Built: 2026-07-15 16:07</t>
+    <t>Built: 2026-08-11 14:53</t>
   </si>
   <si>
     <t>Scope: 48 contiguous U.S. states + DC, vehicle stock counts, 2024 baseline</t>
@@ -80,7 +80,7 @@
     <t>Methodology: docs/methodology/state-vehicles-2024.md</t>
   </si>
   <si>
-    <t>Generator: outputs/transport/_build_state_vehicles_workbook.py</t>
+    <t>Generator: outputs/SYVbT/_build_syvbt_v1_helpers.py</t>
   </si>
   <si>
     <t>Data tabs (sources)</t>
@@ -140,7 +140,7 @@
     <t>State_lookup</t>
   </si>
   <si>
-    <t>Per-state input lookups (FHWA + AFDC + non-road shares).</t>
+    <t>Per-state input lookups (FHWA + AFDC + non-road shares); FHWA envelope re-anchored to AFDC for Keys!stock_fix_states (NY/MT/DE, sec 9.6).</t>
   </si>
   <si>
     <t>National_totals</t>
@@ -215,7 +215,7 @@
     <t>Generator:</t>
   </si>
   <si>
-    <t>outputs/transport/_build_state_vehicles_workbook_v2.py</t>
+    <t>outputs/SYVbT/_build_syvbt_workbook.py</t>
   </si>
   <si>
     <t>Colorado</t>
@@ -521,7 +521,7 @@
     <t>State Vehicles 2024 v2 — Direct-State-Data Variant</t>
   </si>
   <si>
-    <t>Built: 2026-07-15</t>
+    <t>Built: 2026-08-11</t>
   </si>
   <si>
     <t>Goal</t>
@@ -587,7 +587,7 @@
     <t>Build command</t>
   </si>
   <si>
-    <t>python outputs/transport/_build_state_vehicles_workbook_v2.py</t>
+    <t>python outputs/SYVbT/_build_syvbt_workbook.py</t>
   </si>
   <si>
     <t>category</t>
@@ -1055,6 +1055,42 @@
     <t>Aircraft floor per state, carried over from existing transport workbook. Below this, downstream EPS energy-per-vehicle calcs hit divide-by-zero.</t>
   </si>
   <si>
+    <t>min_frgt_ships_rfacb_state</t>
+  </si>
+  <si>
+    <t>Freight-ship floor for states with nonzero SEDS transport residual fuel (State_lookup col X). Same failure mode as the aircraft floor: the BTS top-50-ports share source gives a state with only mid-size ports (Michigan) share 0, and BAADTbVT back-solves ship mileage from RFACB/ships, which silently collapses to zero fuel at 0 ships instead of dividing by zero. One ship is sufficient -- the back-solve then lands the state on its RFACB automatically. Added 2026-08-11 (docs/findings/transport-ships-residual-allocation-2026-08-11.md); affects MI ME DE NC RI VT.</t>
+  </si>
+  <si>
+    <t>fhwa_fix</t>
+  </si>
+  <si>
+    <t>stock_fix_states</t>
+  </si>
+  <si>
+    <t>New York, Montana, Delaware</t>
+  </si>
+  <si>
+    <t>Comma-separated state names whose FHWA MV-1 autos+trucks envelope is re-anchored to the AFDC 2024 LDV total (FHWA auto:truck split preserved). See methodology sec 9.6. Blank to disable.</t>
+  </si>
+  <si>
+    <t>afdc_fix</t>
+  </si>
+  <si>
+    <t>phev_fix_state</t>
+  </si>
+  <si>
+    <t>State whose AFDC PHEV count is overridden (PHEV &gt; BEV, contradicted by independent sales data; sole outlier at z=5.4 across 49 states). PHEV rebuilt as BEV x national PHEV:BEV. Raw AFDC value kept in phev_raw_AFDC. See docs/methodology/state-vehicles-2024.md 9.5. Blank this cell to disable the override.</t>
+  </si>
+  <si>
+    <t>afdc_national_row</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Row label of the national total on the AFDC_state_fuel_2024 source tab, used to derive the national PHEV:BEV ratio for the override.</t>
+  </si>
+  <si>
     <t>passenger LDVs — vehicles 2024 (v2 direct-state)</t>
   </si>
   <si>
@@ -1157,6 +1193,21 @@
     <t>motorbikes_total</t>
   </si>
   <si>
+    <t>fhwa_autos_raw</t>
+  </si>
+  <si>
+    <t>fhwa_trucks_raw</t>
+  </si>
+  <si>
+    <t>afdc_ldv_total</t>
+  </si>
+  <si>
+    <t>stock_override?</t>
+  </si>
+  <si>
+    <t>transport_RFACB_2024_bbtu</t>
+  </si>
+  <si>
     <t>SUM</t>
   </si>
   <si>
@@ -1166,7 +1217,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>AFDC 2024 state × EPS fuel-tech lookup. Source: AFDC_state_fuel_2024 tab (= afdc.energy.gov/vehicle-registration, retrieved 2026-06). Per the AFDC→EPS crosswalk: HEV + E85 + Methanol → gasoline; Biodiesel → diesel; Unknown distributed pro-rata to gasoline/diesel. DIESEL is rescaled: AEO_national_LDV_diesel × (AFDC_state_dsl_broad / AFDC_US_dsl_broad) to match EPS's narrower "TDI Diesel ICE" definition. See methodology §9.2.</t>
+    <t>AFDC 2024 state × EPS fuel-tech lookup. Source: AFDC_state_fuel_2024 tab (= afdc.energy.gov/vehicle-registration, retrieved 2026-06). Per the AFDC→EPS crosswalk: HEV + E85 + Methanol → gasoline; Biodiesel → diesel; Unknown distributed pro-rata to gasoline/diesel. DIESEL is rescaled: AEO_national_LDV_diesel × (AFDC_state_dsl_broad / AFDC_US_dsl_broad) to match EPS's narrower "TDI Diesel ICE" definition (methodology §9.2). PHEV: col L is the raw AFDC value; col D is what SSYVbT reads and carries a documented override for the state named on Keys!phev_fix_state (Oklahoma — AFDC reports PHEV &gt; BEV there, contradicted by independent sales data; rebuilt as BEV × national PHEV:BEV). Col M flags the overridden row. See methodology §9.5.</t>
   </si>
   <si>
     <t>unknown_total</t>
@@ -1175,6 +1226,12 @@
     <t>dsl_raw_AFDC</t>
   </si>
   <si>
+    <t>phev_raw_AFDC</t>
+  </si>
+  <si>
+    <t>phev_override?</t>
+  </si>
+  <si>
     <t>state_fips</t>
   </si>
   <si>
@@ -1599,9 +1656,6 @@
   </si>
   <si>
     <t>Unknown Fuel</t>
-  </si>
-  <si>
-    <t>United States</t>
   </si>
   <si>
     <t>% of total calculated from DOT veh registrations</t>
@@ -2144,7 +2198,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -2287,7 +2341,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -3950,7 +4004,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
@@ -3983,7 +4037,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$7</f>
@@ -4016,7 +4070,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
@@ -4063,7 +4117,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -4303,27 +4357,27 @@
       </c>
       <c r="B9">
         <f>ROUND(State_lookup!E8*Keys!$C$32*Keys!$C$29*(National_totals!$C$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="C9">
         <f>ROUND(State_lookup!E8*Keys!$C$32*Keys!$C$29*(National_totals!$D$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <f>ROUND(State_lookup!E8*Keys!$C$32*Keys!$C$29*(National_totals!$E$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>6275</v>
+        <v>13780</v>
       </c>
       <c r="E9">
         <f>ROUND(State_lookup!E8*Keys!$C$32*Keys!$C$29*(National_totals!$F$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>5363</v>
+        <v>11777</v>
       </c>
       <c r="F9">
         <f>ROUND(State_lookup!E8*Keys!$C$32*Keys!$C$29*(National_totals!$G$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <f>ROUND(State_lookup!E8*Keys!$C$32*Keys!$C$29*(National_totals!$H$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <f>ROUND(State_lookup!E8*Keys!$C$32*Keys!$C$29*(National_totals!$I$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
@@ -4881,19 +4935,19 @@
       </c>
       <c r="B26">
         <f>ROUND(State_lookup!E25*Keys!$C$32*Keys!$C$29*(National_totals!$C$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>374</v>
+        <v>192</v>
       </c>
       <c r="C26">
         <f>ROUND(State_lookup!E25*Keys!$C$32*Keys!$C$29*(National_totals!$D$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D26">
         <f>ROUND(State_lookup!E25*Keys!$C$32*Keys!$C$29*(National_totals!$E$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>34677</v>
+        <v>17832</v>
       </c>
       <c r="E26">
         <f>ROUND(State_lookup!E25*Keys!$C$32*Keys!$C$29*(National_totals!$F$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>29637</v>
+        <v>15240</v>
       </c>
       <c r="F26">
         <f>ROUND(State_lookup!E25*Keys!$C$32*Keys!$C$29*(National_totals!$G$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
@@ -4901,7 +4955,7 @@
       </c>
       <c r="G26">
         <f>ROUND(State_lookup!E25*Keys!$C$32*Keys!$C$29*(National_totals!$H$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H26">
         <f>ROUND(State_lookup!E25*Keys!$C$32*Keys!$C$29*(National_totals!$I$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
@@ -5085,27 +5139,27 @@
       </c>
       <c r="B32">
         <f>ROUND(State_lookup!E31*Keys!$C$32*Keys!$C$29*(National_totals!$C$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>3382</v>
+        <v>1916</v>
       </c>
       <c r="C32">
         <f>ROUND(State_lookup!E31*Keys!$C$32*Keys!$C$29*(National_totals!$D$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>618</v>
+        <v>350</v>
       </c>
       <c r="D32">
         <f>ROUND(State_lookup!E31*Keys!$C$32*Keys!$C$29*(National_totals!$E$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>313859</v>
+        <v>177785</v>
       </c>
       <c r="E32">
         <f>ROUND(State_lookup!E31*Keys!$C$32*Keys!$C$29*(National_totals!$F$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>268247</v>
+        <v>151948</v>
       </c>
       <c r="F32">
         <f>ROUND(State_lookup!E31*Keys!$C$32*Keys!$C$29*(National_totals!$G$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G32">
         <f>ROUND(State_lookup!E31*Keys!$C$32*Keys!$C$29*(National_totals!$H$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="H32">
         <f>ROUND(State_lookup!E31*Keys!$C$32*Keys!$C$29*(National_totals!$I$8/SUM(National_totals!$C$8:$I$8)), 0)</f>
@@ -5726,31 +5780,31 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
-        <v>47072</v>
+        <v>45504</v>
       </c>
       <c r="C51" s="4">
         <f t="shared" si="0"/>
-        <v>8600</v>
+        <v>8314</v>
       </c>
       <c r="D51" s="4">
         <f t="shared" si="0"/>
-        <v>4368346</v>
+        <v>4222932</v>
       </c>
       <c r="E51" s="4">
         <f t="shared" si="0"/>
-        <v>3733503</v>
+        <v>3609221</v>
       </c>
       <c r="F51" s="4">
         <f t="shared" si="0"/>
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G51" s="4">
         <f t="shared" si="0"/>
-        <v>763</v>
+        <v>737</v>
       </c>
       <c r="H51" s="4">
         <f t="shared" si="0"/>
@@ -5759,7 +5813,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$8</f>
@@ -5792,31 +5846,31 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
-        <v>-0.65961877765886678</v>
+        <v>-0.67095710525554619</v>
       </c>
       <c r="C53" s="7">
         <f t="shared" si="1"/>
-        <v>-0.65963509716230662</v>
+        <v>-0.67095420904737402</v>
       </c>
       <c r="D53" s="7">
         <f t="shared" si="1"/>
-        <v>-0.65961952560112169</v>
+        <v>-0.67095014966438016</v>
       </c>
       <c r="E53" s="7">
         <f t="shared" si="1"/>
-        <v>-0.65961959294966854</v>
+        <v>-0.67095028097885434</v>
       </c>
       <c r="F53" s="7">
         <f t="shared" si="1"/>
-        <v>-0.66531440162271804</v>
+        <v>-0.67342799188640978</v>
       </c>
       <c r="G53" s="7">
         <f t="shared" si="1"/>
-        <v>-0.65907059874888296</v>
+        <v>-0.67068811438784626</v>
       </c>
       <c r="H53" s="7">
         <f t="shared" si="1"/>
@@ -5839,7 +5893,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -6079,19 +6133,19 @@
       </c>
       <c r="B9">
         <f>ROUND(State_lookup!E8*Keys!$C$31*(National_totals!$C$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <f>ROUND(State_lookup!E8*Keys!$C$31*(National_totals!$D$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>103</v>
+        <v>227</v>
       </c>
       <c r="D9">
         <f>ROUND(State_lookup!E8*Keys!$C$31*(National_totals!$E$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="E9">
         <f>ROUND(State_lookup!E8*Keys!$C$31*(National_totals!$F$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>9824</v>
+        <v>21575</v>
       </c>
       <c r="F9">
         <f>ROUND(State_lookup!E8*Keys!$C$31*(National_totals!$G$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
@@ -6099,7 +6153,7 @@
       </c>
       <c r="G9">
         <f>ROUND(State_lookup!E8*Keys!$C$31*(National_totals!$H$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H9">
         <f>ROUND(State_lookup!E8*Keys!$C$31*(National_totals!$I$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
@@ -6657,19 +6711,19 @@
       </c>
       <c r="B26">
         <f>ROUND(State_lookup!E25*Keys!$C$31*(National_totals!$C$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C26">
         <f>ROUND(State_lookup!E25*Keys!$C$31*(National_totals!$D$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>571</v>
+        <v>294</v>
       </c>
       <c r="D26">
         <f>ROUND(State_lookup!E25*Keys!$C$31*(National_totals!$E$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>380</v>
+        <v>195</v>
       </c>
       <c r="E26">
         <f>ROUND(State_lookup!E25*Keys!$C$31*(National_totals!$F$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>54293</v>
+        <v>27919</v>
       </c>
       <c r="F26">
         <f>ROUND(State_lookup!E25*Keys!$C$31*(National_totals!$G$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
@@ -6677,7 +6731,7 @@
       </c>
       <c r="G26">
         <f>ROUND(State_lookup!E25*Keys!$C$31*(National_totals!$H$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H26">
         <f>ROUND(State_lookup!E25*Keys!$C$31*(National_totals!$I$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
@@ -6861,19 +6915,19 @@
       </c>
       <c r="B32">
         <f>ROUND(State_lookup!E31*Keys!$C$31*(National_totals!$C$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>190</v>
+        <v>108</v>
       </c>
       <c r="C32">
         <f>ROUND(State_lookup!E31*Keys!$C$31*(National_totals!$D$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>5172</v>
+        <v>2930</v>
       </c>
       <c r="D32">
         <f>ROUND(State_lookup!E31*Keys!$C$31*(National_totals!$E$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>3437</v>
+        <v>1947</v>
       </c>
       <c r="E32">
         <f>ROUND(State_lookup!E31*Keys!$C$31*(National_totals!$F$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>491408</v>
+        <v>278357</v>
       </c>
       <c r="F32">
         <f>ROUND(State_lookup!E31*Keys!$C$31*(National_totals!$G$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
@@ -6881,7 +6935,7 @@
       </c>
       <c r="G32">
         <f>ROUND(State_lookup!E31*Keys!$C$31*(National_totals!$H$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
-        <v>275</v>
+        <v>156</v>
       </c>
       <c r="H32">
         <f>ROUND(State_lookup!E31*Keys!$C$31*(National_totals!$I$9/SUM(National_totals!$C$9:$I$9)), 0)</f>
@@ -7502,23 +7556,23 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
-        <v>2650</v>
+        <v>2562</v>
       </c>
       <c r="C51" s="4">
         <f t="shared" si="0"/>
-        <v>71979</v>
+        <v>69584</v>
       </c>
       <c r="D51" s="4">
         <f t="shared" si="0"/>
-        <v>47830</v>
+        <v>46237</v>
       </c>
       <c r="E51" s="4">
         <f t="shared" si="0"/>
-        <v>6839492</v>
+        <v>6611818</v>
       </c>
       <c r="F51" s="4">
         <f t="shared" si="0"/>
@@ -7526,7 +7580,7 @@
       </c>
       <c r="G51" s="4">
         <f t="shared" si="0"/>
-        <v>3836</v>
+        <v>3709</v>
       </c>
       <c r="H51" s="4">
         <f t="shared" si="0"/>
@@ -7535,7 +7589,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$9</f>
@@ -7568,23 +7622,23 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
-        <v>0.25354777672658468</v>
+        <v>0.2119205298013245</v>
       </c>
       <c r="C53" s="7">
         <f t="shared" si="1"/>
-        <v>0.25416434346250349</v>
+        <v>0.21243378868134932</v>
       </c>
       <c r="D53" s="7">
         <f t="shared" si="1"/>
-        <v>0.25419551080344033</v>
+        <v>0.21242395636668765</v>
       </c>
       <c r="E53" s="7">
         <f t="shared" si="1"/>
-        <v>0.25421095011152123</v>
+        <v>0.2124605944044467</v>
       </c>
       <c r="F53" s="7">
         <f t="shared" si="1"/>
@@ -7592,7 +7646,7 @@
       </c>
       <c r="G53" s="7">
         <f t="shared" si="1"/>
-        <v>0.25482499182204776</v>
+        <v>0.21328099443899248</v>
       </c>
       <c r="H53" s="7">
         <f t="shared" si="1"/>
@@ -7615,7 +7669,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -9278,7 +9332,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
@@ -9311,7 +9365,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$10</f>
@@ -9344,7 +9398,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
@@ -9391,7 +9445,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -11054,7 +11108,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
@@ -11087,7 +11141,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$11</f>
@@ -11120,7 +11174,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
@@ -11167,7 +11221,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -11214,7 +11268,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <f>IFERROR(ROUND(State_lookup!N2/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X2&gt;0,MAX(State_lookup!N2/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N2/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>4</v>
       </c>
       <c r="F3">
@@ -11248,7 +11302,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <f>IFERROR(ROUND(State_lookup!N3/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X3&gt;0,MAX(State_lookup!N3/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N3/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F4">
@@ -11282,7 +11336,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <f>IFERROR(ROUND(State_lookup!N4/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X4&gt;0,MAX(State_lookup!N4/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N4/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F5">
@@ -11316,7 +11370,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <f>IFERROR(ROUND(State_lookup!N5/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X5&gt;0,MAX(State_lookup!N5/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N5/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>14</v>
       </c>
       <c r="F6">
@@ -11350,7 +11404,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <f>IFERROR(ROUND(State_lookup!N6/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X6&gt;0,MAX(State_lookup!N6/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N6/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F7">
@@ -11384,7 +11438,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <f>IFERROR(ROUND(State_lookup!N7/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X7&gt;0,MAX(State_lookup!N7/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N7/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F8">
@@ -11418,8 +11472,8 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <f>IFERROR(ROUND(State_lookup!N8/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(IF(State_lookup!X8&gt;0,MAX(State_lookup!N8/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N8/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
+        <v>1</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(State_lookup!N8/SUM(State_lookup!N2:N49)*National_totals!$G$12, 0), 0)</f>
@@ -11452,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <f>IFERROR(ROUND(State_lookup!N9/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X9&gt;0,MAX(State_lookup!N9/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N9/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>5</v>
       </c>
       <c r="F10">
@@ -11486,7 +11540,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <f>IFERROR(ROUND(State_lookup!N10/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X10&gt;0,MAX(State_lookup!N10/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N10/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>3</v>
       </c>
       <c r="F11">
@@ -11520,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <f>IFERROR(ROUND(State_lookup!N11/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X11&gt;0,MAX(State_lookup!N11/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N11/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F12">
@@ -11554,7 +11608,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <f>IFERROR(ROUND(State_lookup!N12/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X12&gt;0,MAX(State_lookup!N12/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N12/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>3</v>
       </c>
       <c r="F13">
@@ -11588,7 +11642,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <f>IFERROR(ROUND(State_lookup!N13/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X13&gt;0,MAX(State_lookup!N13/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N13/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>2</v>
       </c>
       <c r="F14">
@@ -11622,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <f>IFERROR(ROUND(State_lookup!N14/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X14&gt;0,MAX(State_lookup!N14/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N14/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F15">
@@ -11656,7 +11710,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <f>IFERROR(ROUND(State_lookup!N15/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X15&gt;0,MAX(State_lookup!N15/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N15/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F16">
@@ -11690,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <f>IFERROR(ROUND(State_lookup!N16/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X16&gt;0,MAX(State_lookup!N16/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N16/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>3</v>
       </c>
       <c r="F17">
@@ -11724,7 +11778,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <f>IFERROR(ROUND(State_lookup!N17/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X17&gt;0,MAX(State_lookup!N17/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N17/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>36</v>
       </c>
       <c r="F18">
@@ -11758,8 +11812,8 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <f>IFERROR(ROUND(State_lookup!N18/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(IF(State_lookup!X18&gt;0,MAX(State_lookup!N18/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N18/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
+        <v>1</v>
       </c>
       <c r="F19">
         <f>IFERROR(ROUND(State_lookup!N18/SUM(State_lookup!N2:N49)*National_totals!$G$12, 0), 0)</f>
@@ -11792,7 +11846,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <f>IFERROR(ROUND(State_lookup!N19/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X19&gt;0,MAX(State_lookup!N19/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N19/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>3</v>
       </c>
       <c r="F20">
@@ -11826,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <f>IFERROR(ROUND(State_lookup!N20/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X20&gt;0,MAX(State_lookup!N20/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N20/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>1</v>
       </c>
       <c r="F21">
@@ -11860,8 +11914,8 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <f>IFERROR(ROUND(State_lookup!N21/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(IF(State_lookup!X21&gt;0,MAX(State_lookup!N21/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N21/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
+        <v>1</v>
       </c>
       <c r="F22">
         <f>IFERROR(ROUND(State_lookup!N21/SUM(State_lookup!N2:N49)*National_totals!$G$12, 0), 0)</f>
@@ -11894,7 +11948,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <f>IFERROR(ROUND(State_lookup!N22/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X22&gt;0,MAX(State_lookup!N22/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N22/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>2</v>
       </c>
       <c r="F23">
@@ -11928,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <f>IFERROR(ROUND(State_lookup!N23/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X23&gt;0,MAX(State_lookup!N23/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N23/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>2</v>
       </c>
       <c r="F24">
@@ -11962,7 +12016,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <f>IFERROR(ROUND(State_lookup!N24/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X24&gt;0,MAX(State_lookup!N24/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N24/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>2</v>
       </c>
       <c r="F25">
@@ -11996,7 +12050,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <f>IFERROR(ROUND(State_lookup!N25/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X25&gt;0,MAX(State_lookup!N25/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N25/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F26">
@@ -12030,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <f>IFERROR(ROUND(State_lookup!N26/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X26&gt;0,MAX(State_lookup!N26/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N26/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F27">
@@ -12064,7 +12118,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <f>IFERROR(ROUND(State_lookup!N27/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X27&gt;0,MAX(State_lookup!N27/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N27/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F28">
@@ -12098,7 +12152,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <f>IFERROR(ROUND(State_lookup!N28/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X28&gt;0,MAX(State_lookup!N28/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N28/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F29">
@@ -12132,7 +12186,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <f>IFERROR(ROUND(State_lookup!N29/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X29&gt;0,MAX(State_lookup!N29/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N29/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>6</v>
       </c>
       <c r="F30">
@@ -12166,7 +12220,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <f>IFERROR(ROUND(State_lookup!N30/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X30&gt;0,MAX(State_lookup!N30/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N30/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F31">
@@ -12200,7 +12254,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <f>IFERROR(ROUND(State_lookup!N31/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X31&gt;0,MAX(State_lookup!N31/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N31/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>5</v>
       </c>
       <c r="F32">
@@ -12234,8 +12288,8 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <f>IFERROR(ROUND(State_lookup!N32/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(IF(State_lookup!X32&gt;0,MAX(State_lookup!N32/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N32/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
+        <v>1</v>
       </c>
       <c r="F33">
         <f>IFERROR(ROUND(State_lookup!N32/SUM(State_lookup!N2:N49)*National_totals!$G$12, 0), 0)</f>
@@ -12268,7 +12322,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <f>IFERROR(ROUND(State_lookup!N33/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X33&gt;0,MAX(State_lookup!N33/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N33/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F34">
@@ -12302,7 +12356,7 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <f>IFERROR(ROUND(State_lookup!N34/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X34&gt;0,MAX(State_lookup!N34/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N34/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>2</v>
       </c>
       <c r="F35">
@@ -12336,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <f>IFERROR(ROUND(State_lookup!N35/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X35&gt;0,MAX(State_lookup!N35/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N35/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F36">
@@ -12370,7 +12424,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <f>IFERROR(ROUND(State_lookup!N36/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X36&gt;0,MAX(State_lookup!N36/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N36/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>2</v>
       </c>
       <c r="F37">
@@ -12404,7 +12458,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <f>IFERROR(ROUND(State_lookup!N37/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X37&gt;0,MAX(State_lookup!N37/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N37/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>3</v>
       </c>
       <c r="F38">
@@ -12438,8 +12492,8 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <f>IFERROR(ROUND(State_lookup!N38/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(IF(State_lookup!X38&gt;0,MAX(State_lookup!N38/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N38/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
+        <v>1</v>
       </c>
       <c r="F39">
         <f>IFERROR(ROUND(State_lookup!N38/SUM(State_lookup!N2:N49)*National_totals!$G$12, 0), 0)</f>
@@ -12472,7 +12526,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <f>IFERROR(ROUND(State_lookup!N39/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X39&gt;0,MAX(State_lookup!N39/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N39/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>2</v>
       </c>
       <c r="F40">
@@ -12506,7 +12560,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <f>IFERROR(ROUND(State_lookup!N40/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X40&gt;0,MAX(State_lookup!N40/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N40/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F41">
@@ -12540,8 +12594,8 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <f>IFERROR(ROUND(State_lookup!N41/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(IF(State_lookup!X41&gt;0,MAX(State_lookup!N41/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N41/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
+        <v>1</v>
       </c>
       <c r="F42">
         <f>IFERROR(ROUND(State_lookup!N41/SUM(State_lookup!N2:N49)*National_totals!$G$12, 0), 0)</f>
@@ -12574,7 +12628,7 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <f>IFERROR(ROUND(State_lookup!N42/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X42&gt;0,MAX(State_lookup!N42/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N42/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>48</v>
       </c>
       <c r="F43">
@@ -12608,7 +12662,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <f>IFERROR(ROUND(State_lookup!N43/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X43&gt;0,MAX(State_lookup!N43/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N43/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F44">
@@ -12642,8 +12696,8 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <f>IFERROR(ROUND(State_lookup!N44/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(IF(State_lookup!X44&gt;0,MAX(State_lookup!N44/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N44/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
+        <v>1</v>
       </c>
       <c r="F45">
         <f>IFERROR(ROUND(State_lookup!N44/SUM(State_lookup!N2:N49)*National_totals!$G$12, 0), 0)</f>
@@ -12676,7 +12730,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <f>IFERROR(ROUND(State_lookup!N45/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X45&gt;0,MAX(State_lookup!N45/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N45/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>4</v>
       </c>
       <c r="F46">
@@ -12710,7 +12764,7 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <f>IFERROR(ROUND(State_lookup!N46/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X46&gt;0,MAX(State_lookup!N46/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N46/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>6</v>
       </c>
       <c r="F47">
@@ -12744,7 +12798,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <f>IFERROR(ROUND(State_lookup!N47/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X47&gt;0,MAX(State_lookup!N47/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N47/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>4</v>
       </c>
       <c r="F48">
@@ -12778,7 +12832,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <f>IFERROR(ROUND(State_lookup!N48/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X48&gt;0,MAX(State_lookup!N48/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N48/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>1</v>
       </c>
       <c r="F49">
@@ -12812,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <f>IFERROR(ROUND(State_lookup!N49/SUM(State_lookup!N2:N49)*National_totals!$F$12, 0), 0)</f>
+        <f>IFERROR(ROUND(IF(State_lookup!X49&gt;0,MAX(State_lookup!N49/SUM(State_lookup!N2:N49)*National_totals!$F$12, Keys!$C$60),State_lookup!N49/SUM(State_lookup!N2:N49)*National_totals!$F$12), 0), 0)</f>
         <v>0</v>
       </c>
       <c r="F50">
@@ -12830,7 +12884,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
@@ -12846,7 +12900,7 @@
       </c>
       <c r="E51" s="4">
         <f t="shared" si="0"/>
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F51" s="4">
         <f t="shared" si="0"/>
@@ -12863,7 +12917,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$12</f>
@@ -12896,7 +12950,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
@@ -12912,7 +12966,7 @@
       </c>
       <c r="E53" s="7">
         <f t="shared" si="1"/>
-        <v>-6.0975609756097563E-3</v>
+        <v>3.6585365853658534E-2</v>
       </c>
       <c r="F53" s="7">
         <f t="shared" si="1"/>
@@ -12943,7 +12997,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -14606,7 +14660,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
@@ -14639,7 +14693,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$13</f>
@@ -14672,7 +14726,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
@@ -14710,74 +14764,89 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:X50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="19" width="18" customWidth="1"/>
+    <col min="3" max="24" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+        <v>367</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -14786,7 +14855,7 @@
         <v>Alabama</v>
       </c>
       <c r="C2">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B2&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B2&amp;",", ", "&amp;Keys!$C$61&amp;",")), V2*T2/(T2+U2), T2)</f>
         <v>1937330</v>
       </c>
       <c r="D2">
@@ -14794,7 +14863,7 @@
         <v>3369</v>
       </c>
       <c r="E2">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B2&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B2&amp;",", ", "&amp;Keys!$C$61&amp;",")), V2*U2/(T2+U2), U2)</f>
         <v>3585631</v>
       </c>
       <c r="F2">
@@ -14853,8 +14922,27 @@
         <f t="shared" ref="S2:S49" si="1">F2</f>
         <v>129014</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T2">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B2&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1937330</v>
+      </c>
+      <c r="U2">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B2&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3585631</v>
+      </c>
+      <c r="V2">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B2, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>4881700</v>
+      </c>
+      <c r="W2" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B2&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <v>4465</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -14863,7 +14951,7 @@
         <v>Arizona</v>
       </c>
       <c r="C3">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B3&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B3&amp;",", ", "&amp;Keys!$C$61&amp;",")), V3*T3/(T3+U3), T3)</f>
         <v>2287531</v>
       </c>
       <c r="D3">
@@ -14871,7 +14959,7 @@
         <v>22617</v>
       </c>
       <c r="E3">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B3&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B3&amp;",", ", "&amp;Keys!$C$61&amp;",")), V3*U3/(T3+U3), U3)</f>
         <v>4090469</v>
       </c>
       <c r="F3">
@@ -14930,8 +15018,27 @@
         <f t="shared" si="1"/>
         <v>292014</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T3">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B3&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2287531</v>
+      </c>
+      <c r="U3">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B3&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>4090469</v>
+      </c>
+      <c r="V3">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B3, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>6586900</v>
+      </c>
+      <c r="W3" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B3&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -14940,7 +15047,7 @@
         <v>Arkansas</v>
       </c>
       <c r="C4">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B4&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B4&amp;",", ", "&amp;Keys!$C$61&amp;",")), V4*T4/(T4+U4), T4)</f>
         <v>911769</v>
       </c>
       <c r="D4">
@@ -14948,7 +15055,7 @@
         <v>10805</v>
       </c>
       <c r="E4">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B4&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B4&amp;",", ", "&amp;Keys!$C$61&amp;",")), V4*U4/(T4+U4), U4)</f>
         <v>2343579</v>
       </c>
       <c r="F4">
@@ -15007,8 +15114,27 @@
         <f t="shared" si="1"/>
         <v>100497</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T4">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B4&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>911769</v>
+      </c>
+      <c r="U4">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B4&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2343579</v>
+      </c>
+      <c r="V4">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B4, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>2737200</v>
+      </c>
+      <c r="W4" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B4&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -15017,7 +15143,7 @@
         <v>California</v>
       </c>
       <c r="C5">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B5&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B5&amp;",", ", "&amp;Keys!$C$61&amp;",")), V5*T5/(T5+U5), T5)</f>
         <v>12979522</v>
       </c>
       <c r="D5">
@@ -15025,7 +15151,7 @@
         <v>96229</v>
       </c>
       <c r="E5">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B5&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B5&amp;",", ", "&amp;Keys!$C$61&amp;",")), V5*U5/(T5+U5), U5)</f>
         <v>17113763</v>
       </c>
       <c r="F5">
@@ -15084,8 +15210,27 @@
         <f t="shared" si="1"/>
         <v>751138</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T5">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B5&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>12979522</v>
+      </c>
+      <c r="U5">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B5&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>17113763</v>
+      </c>
+      <c r="V5">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B5, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>37428700</v>
+      </c>
+      <c r="W5" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B5&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <v>163526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -15094,7 +15239,7 @@
         <v>Colorado</v>
       </c>
       <c r="C6">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B6&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B6&amp;",", ", "&amp;Keys!$C$61&amp;",")), V6*T6/(T6+U6), T6)</f>
         <v>1356526</v>
       </c>
       <c r="D6">
@@ -15102,7 +15247,7 @@
         <v>12602</v>
       </c>
       <c r="E6">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B6&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B6&amp;",", ", "&amp;Keys!$C$61&amp;",")), V6*U6/(T6+U6), U6)</f>
         <v>3731091</v>
       </c>
       <c r="F6">
@@ -15161,8 +15306,27 @@
         <f t="shared" si="1"/>
         <v>176484</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T6">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B6&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1356526</v>
+      </c>
+      <c r="U6">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B6&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3731091</v>
+      </c>
+      <c r="V6">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B6, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>5494000</v>
+      </c>
+      <c r="W6" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B6&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -15171,7 +15335,7 @@
         <v>Connecticut</v>
       </c>
       <c r="C7">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B7&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B7&amp;",", ", "&amp;Keys!$C$61&amp;",")), V7*T7/(T7+U7), T7)</f>
         <v>1028799</v>
       </c>
       <c r="D7">
@@ -15179,7 +15343,7 @@
         <v>9889</v>
       </c>
       <c r="E7">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B7&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B7&amp;",", ", "&amp;Keys!$C$61&amp;",")), V7*U7/(T7+U7), U7)</f>
         <v>1688772</v>
       </c>
       <c r="F7">
@@ -15238,8 +15402,27 @@
         <f t="shared" si="1"/>
         <v>81996</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T7">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B7&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1028799</v>
+      </c>
+      <c r="U7">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B7&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1688772</v>
+      </c>
+      <c r="V7">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B7, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>2922700</v>
+      </c>
+      <c r="W7" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B7&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -15248,16 +15431,16 @@
         <v>Delaware</v>
       </c>
       <c r="C8">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B8&amp;"*", FHWA_MV1!A:A, 0))</f>
-        <v>148493</v>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B8&amp;",", ", "&amp;Keys!$C$61&amp;",")), V8*T8/(T8+U8), T8)</f>
+        <v>326111.28218716354</v>
       </c>
       <c r="D8">
         <f>INDEX(FHWA_MV1!G:G, MATCH(B8&amp;"*", FHWA_MV1!A:A, 0))</f>
         <v>3483</v>
       </c>
       <c r="E8">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B8&amp;"*", FHWA_MV1!A:A, 0))</f>
-        <v>270424</v>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B8&amp;",", ", "&amp;Keys!$C$61&amp;",")), V8*U8/(T8+U8), U8)</f>
+        <v>593888.7178128364</v>
       </c>
       <c r="F8">
         <f>INDEX(FHWA_MV1!M:M, MATCH(B8&amp;"*", FHWA_MV1!A:A, 0))</f>
@@ -15297,7 +15480,7 @@
       </c>
       <c r="O8">
         <f>C8 + E8*Keys!$C$32*Keys!$C$30</f>
-        <v>397192.48796</v>
+        <v>872289.94985450571</v>
       </c>
       <c r="P8">
         <f t="shared" si="0"/>
@@ -15305,18 +15488,37 @@
       </c>
       <c r="Q8">
         <f>E8*Keys!$C$32*Keys!$C$29</f>
-        <v>11718.82404</v>
+        <v>25736.167586419262</v>
       </c>
       <c r="R8">
         <f>E8*Keys!$C$31</f>
-        <v>10005.688</v>
+        <v>21973.882559074947</v>
       </c>
       <c r="S8">
         <f t="shared" si="1"/>
         <v>24694</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T8">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B8&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>148493</v>
+      </c>
+      <c r="U8">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B8&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>270424</v>
+      </c>
+      <c r="V8">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B8, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>920000</v>
+      </c>
+      <c r="W8" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B8&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v>RE-ANCHORED to AFDC (see Keys / methodology 9.6)</v>
+      </c>
+      <c r="X8">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -15325,7 +15527,7 @@
         <v>Florida</v>
       </c>
       <c r="C9">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B9&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B9&amp;",", ", "&amp;Keys!$C$61&amp;",")), V9*T9/(T9+U9), T9)</f>
         <v>7210114</v>
       </c>
       <c r="D9">
@@ -15333,7 +15535,7 @@
         <v>57468</v>
       </c>
       <c r="E9">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B9&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B9&amp;",", ", "&amp;Keys!$C$61&amp;",")), V9*U9/(T9+U9), U9)</f>
         <v>11794134</v>
       </c>
       <c r="F9">
@@ -15392,8 +15594,27 @@
         <f t="shared" si="1"/>
         <v>634364</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T9">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B9&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>7210114</v>
+      </c>
+      <c r="U9">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B9&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>11794134</v>
+      </c>
+      <c r="V9">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B9, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>18742500</v>
+      </c>
+      <c r="W9" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B9&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <v>62768</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -15402,7 +15623,7 @@
         <v>Georgia</v>
       </c>
       <c r="C10">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B10&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B10&amp;",", ", "&amp;Keys!$C$61&amp;",")), V10*T10/(T10+U10), T10)</f>
         <v>3206610</v>
       </c>
       <c r="D10">
@@ -15410,7 +15631,7 @@
         <v>39381</v>
       </c>
       <c r="E10">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B10&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B10&amp;",", ", "&amp;Keys!$C$61&amp;",")), V10*U10/(T10+U10), U10)</f>
         <v>5842123</v>
       </c>
       <c r="F10">
@@ -15469,8 +15690,27 @@
         <f t="shared" si="1"/>
         <v>221294</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T10">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B10&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3206610</v>
+      </c>
+      <c r="U10">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B10&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>5842123</v>
+      </c>
+      <c r="V10">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B10, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>9702400</v>
+      </c>
+      <c r="W10" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B10&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <v>6307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -15479,7 +15719,7 @@
         <v>Idaho</v>
       </c>
       <c r="C11">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B11&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B11&amp;",", ", "&amp;Keys!$C$61&amp;",")), V11*T11/(T11+U11), T11)</f>
         <v>510516</v>
       </c>
       <c r="D11">
@@ -15487,7 +15727,7 @@
         <v>4082</v>
       </c>
       <c r="E11">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B11&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B11&amp;",", ", "&amp;Keys!$C$61&amp;",")), V11*U11/(T11+U11), U11)</f>
         <v>1440556</v>
       </c>
       <c r="F11">
@@ -15546,8 +15786,27 @@
         <f t="shared" si="1"/>
         <v>74915</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T11">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B11&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>510516</v>
+      </c>
+      <c r="U11">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B11&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1440556</v>
+      </c>
+      <c r="V11">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B11, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>2018900</v>
+      </c>
+      <c r="W11" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B11&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -15556,7 +15815,7 @@
         <v>Illinois</v>
       </c>
       <c r="C12">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B12&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B12&amp;",", ", "&amp;Keys!$C$61&amp;",")), V12*T12/(T12+U12), T12)</f>
         <v>3514238</v>
       </c>
       <c r="D12">
@@ -15564,7 +15823,7 @@
         <v>39183</v>
       </c>
       <c r="E12">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B12&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B12&amp;",", ", "&amp;Keys!$C$61&amp;",")), V12*U12/(T12+U12), U12)</f>
         <v>6727333</v>
       </c>
       <c r="F12">
@@ -15623,8 +15882,27 @@
         <f t="shared" si="1"/>
         <v>265273</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T12">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B12&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3514238</v>
+      </c>
+      <c r="U12">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B12&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>6727333</v>
+      </c>
+      <c r="V12">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B12, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>10125700</v>
+      </c>
+      <c r="W12" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B12&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -15633,7 +15911,7 @@
         <v>Indiana</v>
       </c>
       <c r="C13">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B13&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B13&amp;",", ", "&amp;Keys!$C$61&amp;",")), V13*T13/(T13+U13), T13)</f>
         <v>1791108</v>
       </c>
       <c r="D13">
@@ -15641,7 +15919,7 @@
         <v>32361</v>
       </c>
       <c r="E13">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B13&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B13&amp;",", ", "&amp;Keys!$C$61&amp;",")), V13*U13/(T13+U13), U13)</f>
         <v>4073391</v>
       </c>
       <c r="F13">
@@ -15700,8 +15978,27 @@
         <f t="shared" si="1"/>
         <v>203871</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T13">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B13&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1791108</v>
+      </c>
+      <c r="U13">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B13&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>4073391</v>
+      </c>
+      <c r="V13">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B13, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>6214600</v>
+      </c>
+      <c r="W13" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B13&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>74</v>
       </c>
@@ -15710,7 +16007,7 @@
         <v>Iowa</v>
       </c>
       <c r="C14">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B14&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B14&amp;",", ", "&amp;Keys!$C$61&amp;",")), V14*T14/(T14+U14), T14)</f>
         <v>1006994</v>
       </c>
       <c r="D14">
@@ -15718,7 +16015,7 @@
         <v>9167</v>
       </c>
       <c r="E14">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B14&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B14&amp;",", ", "&amp;Keys!$C$61&amp;",")), V14*U14/(T14+U14), U14)</f>
         <v>2647322</v>
       </c>
       <c r="F14">
@@ -15777,8 +16074,27 @@
         <f t="shared" si="1"/>
         <v>193164</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T14">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B14&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1006994</v>
+      </c>
+      <c r="U14">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B14&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2647322</v>
+      </c>
+      <c r="V14">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B14, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>3174500</v>
+      </c>
+      <c r="W14" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B14&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -15787,7 +16103,7 @@
         <v>Kansas</v>
       </c>
       <c r="C15">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B15&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B15&amp;",", ", "&amp;Keys!$C$61&amp;",")), V15*T15/(T15+U15), T15)</f>
         <v>594786</v>
       </c>
       <c r="D15">
@@ -15795,7 +16111,7 @@
         <v>1434</v>
       </c>
       <c r="E15">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B15&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B15&amp;",", ", "&amp;Keys!$C$61&amp;",")), V15*U15/(T15+U15), U15)</f>
         <v>1316870</v>
       </c>
       <c r="F15">
@@ -15854,8 +16170,27 @@
         <f t="shared" si="1"/>
         <v>94496</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T15">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B15&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>594786</v>
+      </c>
+      <c r="U15">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B15&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1316870</v>
+      </c>
+      <c r="V15">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B15, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>2649000</v>
+      </c>
+      <c r="W15" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B15&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -15864,7 +16199,7 @@
         <v>Kentucky</v>
       </c>
       <c r="C16">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B16&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B16&amp;",", ", "&amp;Keys!$C$61&amp;",")), V16*T16/(T16+U16), T16)</f>
         <v>1458659</v>
       </c>
       <c r="D16">
@@ -15872,7 +16207,7 @@
         <v>15428</v>
       </c>
       <c r="E16">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B16&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B16&amp;",", ", "&amp;Keys!$C$61&amp;",")), V16*U16/(T16+U16), U16)</f>
         <v>2971565</v>
       </c>
       <c r="F16">
@@ -15931,8 +16266,27 @@
         <f t="shared" si="1"/>
         <v>115887</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T16">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B16&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1458659</v>
+      </c>
+      <c r="U16">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B16&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2971565</v>
+      </c>
+      <c r="V16">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B16, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>3985300</v>
+      </c>
+      <c r="W16" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B16&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -15941,7 +16295,7 @@
         <v>Louisiana</v>
       </c>
       <c r="C17">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B17&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B17&amp;",", ", "&amp;Keys!$C$61&amp;",")), V17*T17/(T17+U17), T17)</f>
         <v>1370563</v>
       </c>
       <c r="D17">
@@ -15949,7 +16303,7 @@
         <v>33629</v>
       </c>
       <c r="E17">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B17&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B17&amp;",", ", "&amp;Keys!$C$61&amp;",")), V17*U17/(T17+U17), U17)</f>
         <v>3046740</v>
       </c>
       <c r="F17">
@@ -16008,8 +16362,27 @@
         <f t="shared" si="1"/>
         <v>105504</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T17">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B17&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1370563</v>
+      </c>
+      <c r="U17">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B17&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3046740</v>
+      </c>
+      <c r="V17">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B17, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>3781900</v>
+      </c>
+      <c r="W17" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B17&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <v>35361</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -16018,7 +16391,7 @@
         <v>Maine</v>
       </c>
       <c r="C18">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B18&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B18&amp;",", ", "&amp;Keys!$C$61&amp;",")), V18*T18/(T18+U18), T18)</f>
         <v>312473</v>
       </c>
       <c r="D18">
@@ -16026,7 +16399,7 @@
         <v>1648</v>
       </c>
       <c r="E18">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B18&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B18&amp;",", ", "&amp;Keys!$C$61&amp;",")), V18*U18/(T18+U18), U18)</f>
         <v>845161</v>
       </c>
       <c r="F18">
@@ -16085,8 +16458,27 @@
         <f t="shared" si="1"/>
         <v>47685</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T18">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B18&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>312473</v>
+      </c>
+      <c r="U18">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B18&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>845161</v>
+      </c>
+      <c r="V18">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B18, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>1256000</v>
+      </c>
+      <c r="W18" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B18&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>87</v>
       </c>
@@ -16095,7 +16487,7 @@
         <v>Maryland</v>
       </c>
       <c r="C19">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B19&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B19&amp;",", ", "&amp;Keys!$C$61&amp;",")), V19*T19/(T19+U19), T19)</f>
         <v>1908452</v>
       </c>
       <c r="D19">
@@ -16103,7 +16495,7 @@
         <v>15907</v>
       </c>
       <c r="E19">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B19&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B19&amp;",", ", "&amp;Keys!$C$61&amp;",")), V19*U19/(T19+U19), U19)</f>
         <v>2942140</v>
       </c>
       <c r="F19">
@@ -16162,8 +16554,27 @@
         <f t="shared" si="1"/>
         <v>99106</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T19">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B19&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1908452</v>
+      </c>
+      <c r="U19">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B19&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2942140</v>
+      </c>
+      <c r="V19">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B19, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>5031900</v>
+      </c>
+      <c r="W19" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B19&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>90</v>
       </c>
@@ -16172,7 +16583,7 @@
         <v>Massachusetts</v>
       </c>
       <c r="C20">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B20&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B20&amp;",", ", "&amp;Keys!$C$61&amp;",")), V20*T20/(T20+U20), T20)</f>
         <v>1706714</v>
       </c>
       <c r="D20">
@@ -16180,7 +16591,7 @@
         <v>13903</v>
       </c>
       <c r="E20">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B20&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B20&amp;",", ", "&amp;Keys!$C$61&amp;",")), V20*U20/(T20+U20), U20)</f>
         <v>3232362</v>
       </c>
       <c r="F20">
@@ -16239,8 +16650,27 @@
         <f t="shared" si="1"/>
         <v>141710</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T20">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B20&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1706714</v>
+      </c>
+      <c r="U20">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B20&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3232362</v>
+      </c>
+      <c r="V20">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B20, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>5534800</v>
+      </c>
+      <c r="W20" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B20&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -16249,7 +16679,7 @@
         <v>Michigan</v>
       </c>
       <c r="C21">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B21&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B21&amp;",", ", "&amp;Keys!$C$61&amp;",")), V21*T21/(T21+U21), T21)</f>
         <v>2494236</v>
       </c>
       <c r="D21">
@@ -16257,7 +16687,7 @@
         <v>2256</v>
       </c>
       <c r="E21">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B21&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B21&amp;",", ", "&amp;Keys!$C$61&amp;",")), V21*U21/(T21+U21), U21)</f>
         <v>6860844</v>
       </c>
       <c r="F21">
@@ -16316,8 +16746,27 @@
         <f t="shared" si="1"/>
         <v>249465</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T21">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B21&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2494236</v>
+      </c>
+      <c r="U21">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B21&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>6860844</v>
+      </c>
+      <c r="V21">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B21, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>8584500</v>
+      </c>
+      <c r="W21" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B21&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <v>4668</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -16326,7 +16775,7 @@
         <v>Minnesota</v>
       </c>
       <c r="C22">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B22&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B22&amp;",", ", "&amp;Keys!$C$61&amp;",")), V22*T22/(T22+U22), T22)</f>
         <v>1609042</v>
       </c>
       <c r="D22">
@@ -16334,7 +16783,7 @@
         <v>14185</v>
       </c>
       <c r="E22">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B22&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B22&amp;",", ", "&amp;Keys!$C$61&amp;",")), V22*U22/(T22+U22), U22)</f>
         <v>4087641</v>
       </c>
       <c r="F22">
@@ -16393,8 +16842,27 @@
         <f t="shared" si="1"/>
         <v>226544</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T22">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B22&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1609042</v>
+      </c>
+      <c r="U22">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B22&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>4087641</v>
+      </c>
+      <c r="V22">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B22, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>5185600</v>
+      </c>
+      <c r="W22" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B22&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -16403,7 +16871,7 @@
         <v>Mississippi</v>
       </c>
       <c r="C23">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B23&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B23&amp;",", ", "&amp;Keys!$C$61&amp;",")), V23*T23/(T23+U23), T23)</f>
         <v>756941</v>
       </c>
       <c r="D23">
@@ -16411,7 +16879,7 @@
         <v>8505</v>
       </c>
       <c r="E23">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B23&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B23&amp;",", ", "&amp;Keys!$C$61&amp;",")), V23*U23/(T23+U23), U23)</f>
         <v>1418382</v>
       </c>
       <c r="F23">
@@ -16470,8 +16938,27 @@
         <f t="shared" si="1"/>
         <v>30421</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T23">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B23&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>756941</v>
+      </c>
+      <c r="U23">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B23&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1418382</v>
+      </c>
+      <c r="V23">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B23, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>2726800</v>
+      </c>
+      <c r="W23" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B23&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>100</v>
       </c>
@@ -16480,7 +16967,7 @@
         <v>Missouri</v>
       </c>
       <c r="C24">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B24&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B24&amp;",", ", "&amp;Keys!$C$61&amp;",")), V24*T24/(T24+U24), T24)</f>
         <v>1645714</v>
       </c>
       <c r="D24">
@@ -16488,7 +16975,7 @@
         <v>22905</v>
       </c>
       <c r="E24">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B24&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B24&amp;",", ", "&amp;Keys!$C$61&amp;",")), V24*U24/(T24+U24), U24)</f>
         <v>3619999</v>
       </c>
       <c r="F24">
@@ -16547,8 +17034,27 @@
         <f t="shared" si="1"/>
         <v>133801</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T24">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B24&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1645714</v>
+      </c>
+      <c r="U24">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B24&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3619999</v>
+      </c>
+      <c r="V24">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B24, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>5726500</v>
+      </c>
+      <c r="W24" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B24&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -16557,16 +17063,16 @@
         <v>Montana</v>
       </c>
       <c r="C25">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B25&amp;"*", FHWA_MV1!A:A, 0))</f>
-        <v>525226</v>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B25&amp;",", ", "&amp;Keys!$C$61&amp;",")), V25*T25/(T25+U25), T25)</f>
+        <v>270089.88160105207</v>
       </c>
       <c r="D25">
         <f>INDEX(FHWA_MV1!G:G, MATCH(B25&amp;"*", FHWA_MV1!A:A, 0))</f>
         <v>5629</v>
       </c>
       <c r="E25">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B25&amp;"*", FHWA_MV1!A:A, 0))</f>
-        <v>1494471</v>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B25&amp;",", ", "&amp;Keys!$C$61&amp;",")), V25*U25/(T25+U25), U25)</f>
+        <v>768510.11839894799</v>
       </c>
       <c r="F25">
         <f>INDEX(FHWA_MV1!M:M, MATCH(B25&amp;"*", FHWA_MV1!A:A, 0))</f>
@@ -16606,7 +17112,7 @@
       </c>
       <c r="O25">
         <f>C25 + E25*Keys!$C$32*Keys!$C$30</f>
-        <v>1899638.6722149998</v>
+        <v>976861.73963842052</v>
       </c>
       <c r="P25">
         <f t="shared" si="0"/>
@@ -16614,18 +17120,37 @@
       </c>
       <c r="Q25">
         <f>E25*Keys!$C$32*Keys!$C$29</f>
-        <v>64762.900784999991</v>
+        <v>33303.385980818413</v>
       </c>
       <c r="R25">
         <f>E25*Keys!$C$31</f>
-        <v>55295.426999999996</v>
+        <v>28434.874380761074</v>
       </c>
       <c r="S25">
         <f t="shared" si="1"/>
         <v>447943</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T25">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B25&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>525226</v>
+      </c>
+      <c r="U25">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B25&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1494471</v>
+      </c>
+      <c r="V25">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B25, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>1038600</v>
+      </c>
+      <c r="W25" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B25&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v>RE-ANCHORED to AFDC (see Keys / methodology 9.6)</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -16634,7 +17159,7 @@
         <v>Nebraska</v>
       </c>
       <c r="C26">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B26&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B26&amp;",", ", "&amp;Keys!$C$61&amp;",")), V26*T26/(T26+U26), T26)</f>
         <v>561111</v>
       </c>
       <c r="D26">
@@ -16642,7 +17167,7 @@
         <v>9006</v>
       </c>
       <c r="E26">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B26&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B26&amp;",", ", "&amp;Keys!$C$61&amp;",")), V26*U26/(T26+U26), U26)</f>
         <v>1368302</v>
       </c>
       <c r="F26">
@@ -16701,8 +17226,27 @@
         <f t="shared" si="1"/>
         <v>50753</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T26">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B26&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>561111</v>
+      </c>
+      <c r="U26">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B26&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1368302</v>
+      </c>
+      <c r="V26">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B26, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>1989600</v>
+      </c>
+      <c r="W26" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B26&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>106</v>
       </c>
@@ -16711,7 +17255,7 @@
         <v>Nevada</v>
       </c>
       <c r="C27">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B27&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B27&amp;",", ", "&amp;Keys!$C$61&amp;",")), V27*T27/(T27+U27), T27)</f>
         <v>843099</v>
       </c>
       <c r="D27">
@@ -16719,7 +17263,7 @@
         <v>7881</v>
       </c>
       <c r="E27">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B27&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B27&amp;",", ", "&amp;Keys!$C$61&amp;",")), V27*U27/(T27+U27), U27)</f>
         <v>1450234</v>
       </c>
       <c r="F27">
@@ -16778,8 +17322,27 @@
         <f t="shared" si="1"/>
         <v>87702</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T27">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B27&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>843099</v>
+      </c>
+      <c r="U27">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B27&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1450234</v>
+      </c>
+      <c r="V27">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B27, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>2607000</v>
+      </c>
+      <c r="W27" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B27&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>108</v>
       </c>
@@ -16788,7 +17351,7 @@
         <v>New Hampshire</v>
       </c>
       <c r="C28">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B28&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B28&amp;",", ", "&amp;Keys!$C$61&amp;",")), V28*T28/(T28+U28), T28)</f>
         <v>391064</v>
       </c>
       <c r="D28">
@@ -16796,7 +17359,7 @@
         <v>2447</v>
       </c>
       <c r="E28">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B28&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B28&amp;",", ", "&amp;Keys!$C$61&amp;",")), V28*U28/(T28+U28), U28)</f>
         <v>910891</v>
       </c>
       <c r="F28">
@@ -16855,8 +17418,27 @@
         <f t="shared" si="1"/>
         <v>86208</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T28">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B28&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>391064</v>
+      </c>
+      <c r="U28">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B28&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>910891</v>
+      </c>
+      <c r="V28">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B28, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>1400600</v>
+      </c>
+      <c r="W28" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B28&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -16865,7 +17447,7 @@
         <v>New Jersey</v>
       </c>
       <c r="C29">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B29&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B29&amp;",", ", "&amp;Keys!$C$61&amp;",")), V29*T29/(T29+U29), T29)</f>
         <v>2275055</v>
       </c>
       <c r="D29">
@@ -16873,7 +17455,7 @@
         <v>25217</v>
       </c>
       <c r="E29">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B29&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B29&amp;",", ", "&amp;Keys!$C$61&amp;",")), V29*U29/(T29+U29), U29)</f>
         <v>3809822</v>
       </c>
       <c r="F29">
@@ -16932,8 +17514,27 @@
         <f t="shared" si="1"/>
         <v>146003</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T29">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B29&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2275055</v>
+      </c>
+      <c r="U29">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B29&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3809822</v>
+      </c>
+      <c r="V29">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B29, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>7426400</v>
+      </c>
+      <c r="W29" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B29&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <v>23811</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>112</v>
       </c>
@@ -16942,7 +17543,7 @@
         <v>New Mexico</v>
       </c>
       <c r="C30">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B30&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B30&amp;",", ", "&amp;Keys!$C$61&amp;",")), V30*T30/(T30+U30), T30)</f>
         <v>590034</v>
       </c>
       <c r="D30">
@@ -16950,7 +17551,7 @@
         <v>7013</v>
       </c>
       <c r="E30">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B30&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B30&amp;",", ", "&amp;Keys!$C$61&amp;",")), V30*U30/(T30+U30), U30)</f>
         <v>1276809</v>
       </c>
       <c r="F30">
@@ -17009,8 +17610,27 @@
         <f t="shared" si="1"/>
         <v>56497</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T30">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B30&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>590034</v>
+      </c>
+      <c r="U30">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B30&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1276809</v>
+      </c>
+      <c r="V30">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B30, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>1955900</v>
+      </c>
+      <c r="W30" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B30&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>114</v>
       </c>
@@ -17019,16 +17639,16 @@
         <v>New York</v>
       </c>
       <c r="C31">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B31&amp;"*", FHWA_MV1!A:A, 0))</f>
-        <v>6474059</v>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B31&amp;",", ", "&amp;Keys!$C$61&amp;",")), V31*T31/(T31+U31), T31)</f>
+        <v>3667217.2648344655</v>
       </c>
       <c r="D31">
         <f>INDEX(FHWA_MV1!G:G, MATCH(B31&amp;"*", FHWA_MV1!A:A, 0))</f>
         <v>195675</v>
       </c>
       <c r="E31">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B31&amp;"*", FHWA_MV1!A:A, 0))</f>
-        <v>13526544</v>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B31&amp;",", ", "&amp;Keys!$C$61&amp;",")), V31*U31/(T31+U31), U31)</f>
+        <v>7662082.7351655345</v>
       </c>
       <c r="F31">
         <f>INDEX(FHWA_MV1!M:M, MATCH(B31&amp;"*", FHWA_MV1!A:A, 0))</f>
@@ -17068,7 +17688,7 @@
       </c>
       <c r="O31">
         <f>C31 + E31*Keys!$C$32*Keys!$C$30</f>
-        <v>18913948.087760001</v>
+        <v>10713766.583470475</v>
       </c>
       <c r="P31">
         <f t="shared" si="0"/>
@@ -17076,18 +17696,37 @@
       </c>
       <c r="Q31">
         <f>E31*Keys!$C$32*Keys!$C$29</f>
-        <v>586172.78423999995</v>
+        <v>332036.35532839841</v>
       </c>
       <c r="R31">
         <f>E31*Keys!$C$31</f>
-        <v>500482.12799999997</v>
+        <v>283497.06120112474</v>
       </c>
       <c r="S31">
         <f t="shared" si="1"/>
         <v>794820</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T31">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B31&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>6474059</v>
+      </c>
+      <c r="U31">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B31&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>13526544</v>
+      </c>
+      <c r="V31">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B31, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>11329300</v>
+      </c>
+      <c r="W31" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B31&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v>RE-ANCHORED to AFDC (see Keys / methodology 9.6)</v>
+      </c>
+      <c r="X31">
+        <v>16750</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>116</v>
       </c>
@@ -17096,7 +17735,7 @@
         <v>North Carolina</v>
       </c>
       <c r="C32">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B32&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B32&amp;",", ", "&amp;Keys!$C$61&amp;",")), V32*T32/(T32+U32), T32)</f>
         <v>3005649</v>
       </c>
       <c r="D32">
@@ -17104,7 +17743,7 @@
         <v>32483</v>
       </c>
       <c r="E32">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B32&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B32&amp;",", ", "&amp;Keys!$C$61&amp;",")), V32*U32/(T32+U32), U32)</f>
         <v>5634554</v>
       </c>
       <c r="F32">
@@ -17163,8 +17802,27 @@
         <f t="shared" si="1"/>
         <v>189734</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T32">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B32&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3005649</v>
+      </c>
+      <c r="U32">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B32&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>5634554</v>
+      </c>
+      <c r="V32">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B32, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>9179700</v>
+      </c>
+      <c r="W32" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B32&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>118</v>
       </c>
@@ -17173,7 +17831,7 @@
         <v>North Dakota</v>
       </c>
       <c r="C33">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B33&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B33&amp;",", ", "&amp;Keys!$C$61&amp;",")), V33*T33/(T33+U33), T33)</f>
         <v>215289</v>
       </c>
       <c r="D33">
@@ -17181,7 +17839,7 @@
         <v>3608</v>
       </c>
       <c r="E33">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B33&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B33&amp;",", ", "&amp;Keys!$C$61&amp;",")), V33*U33/(T33+U33), U33)</f>
         <v>813627</v>
       </c>
       <c r="F33">
@@ -17240,8 +17898,27 @@
         <f t="shared" si="1"/>
         <v>44166</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T33">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B33&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>215289</v>
+      </c>
+      <c r="U33">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B33&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>813627</v>
+      </c>
+      <c r="V33">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B33, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>805900</v>
+      </c>
+      <c r="W33" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B33&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>120</v>
       </c>
@@ -17250,7 +17927,7 @@
         <v>Ohio</v>
       </c>
       <c r="C34">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B34&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B34&amp;",", ", "&amp;Keys!$C$61&amp;",")), V34*T34/(T34+U34), T34)</f>
         <v>3805614</v>
       </c>
       <c r="D34">
@@ -17258,7 +17935,7 @@
         <v>35251</v>
       </c>
       <c r="E34">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B34&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B34&amp;",", ", "&amp;Keys!$C$61&amp;",")), V34*U34/(T34+U34), U34)</f>
         <v>7103426</v>
       </c>
       <c r="F34">
@@ -17317,8 +17994,27 @@
         <f t="shared" si="1"/>
         <v>422404</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T34">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B34&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3805614</v>
+      </c>
+      <c r="U34">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B34&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>7103426</v>
+      </c>
+      <c r="V34">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B34, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>10385000</v>
+      </c>
+      <c r="W34" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B34&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>122</v>
       </c>
@@ -17327,7 +18023,7 @@
         <v>Oklahoma</v>
       </c>
       <c r="C35">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B35&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B35&amp;",", ", "&amp;Keys!$C$61&amp;",")), V35*T35/(T35+U35), T35)</f>
         <v>1061114</v>
       </c>
       <c r="D35">
@@ -17335,7 +18031,7 @@
         <v>2053</v>
       </c>
       <c r="E35">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B35&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B35&amp;",", ", "&amp;Keys!$C$61&amp;",")), V35*U35/(T35+U35), U35)</f>
         <v>2505163</v>
       </c>
       <c r="F35">
@@ -17394,8 +18090,27 @@
         <f t="shared" si="1"/>
         <v>139387</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T35">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B35&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1061114</v>
+      </c>
+      <c r="U35">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B35&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2505163</v>
+      </c>
+      <c r="V35">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B35, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>4238100</v>
+      </c>
+      <c r="W35" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B35&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>124</v>
       </c>
@@ -17404,7 +18119,7 @@
         <v>Oregon</v>
       </c>
       <c r="C36">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B36&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B36&amp;",", ", "&amp;Keys!$C$61&amp;",")), V36*T36/(T36+U36), T36)</f>
         <v>1308985</v>
       </c>
       <c r="D36">
@@ -17412,7 +18127,7 @@
         <v>18183</v>
       </c>
       <c r="E36">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B36&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B36&amp;",", ", "&amp;Keys!$C$61&amp;",")), V36*U36/(T36+U36), U36)</f>
         <v>2784253</v>
       </c>
       <c r="F36">
@@ -17471,8 +18186,27 @@
         <f t="shared" si="1"/>
         <v>143067</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T36">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B36&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1308985</v>
+      </c>
+      <c r="U36">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B36&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2784253</v>
+      </c>
+      <c r="V36">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B36, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>3850200</v>
+      </c>
+      <c r="W36" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B36&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X36">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>126</v>
       </c>
@@ -17481,7 +18215,7 @@
         <v>Pennsylvania</v>
       </c>
       <c r="C37">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B37&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B37&amp;",", ", "&amp;Keys!$C$61&amp;",")), V37*T37/(T37+U37), T37)</f>
         <v>3371581</v>
       </c>
       <c r="D37">
@@ -17489,7 +18223,7 @@
         <v>53789</v>
       </c>
       <c r="E37">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B37&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B37&amp;",", ", "&amp;Keys!$C$61&amp;",")), V37*U37/(T37+U37), U37)</f>
         <v>6844674</v>
       </c>
       <c r="F37">
@@ -17548,8 +18282,27 @@
         <f t="shared" si="1"/>
         <v>342114</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T37">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B37&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3371581</v>
+      </c>
+      <c r="U37">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B37&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>6844674</v>
+      </c>
+      <c r="V37">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B37, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>10245600</v>
+      </c>
+      <c r="W37" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B37&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>128</v>
       </c>
@@ -17558,7 +18311,7 @@
         <v>Rhode Island</v>
       </c>
       <c r="C38">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B38&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B38&amp;",", ", "&amp;Keys!$C$61&amp;",")), V38*T38/(T38+U38), T38)</f>
         <v>308699</v>
       </c>
       <c r="D38">
@@ -17566,7 +18319,7 @@
         <v>2197</v>
       </c>
       <c r="E38">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B38&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B38&amp;",", ", "&amp;Keys!$C$61&amp;",")), V38*U38/(T38+U38), U38)</f>
         <v>502595</v>
       </c>
       <c r="F38">
@@ -17625,8 +18378,27 @@
         <f t="shared" si="1"/>
         <v>25375</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T38">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B38&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>308699</v>
+      </c>
+      <c r="U38">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B38&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>502595</v>
+      </c>
+      <c r="V38">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B38, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>872100</v>
+      </c>
+      <c r="W38" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B38&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X38">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>130</v>
       </c>
@@ -17635,7 +18407,7 @@
         <v>South Carolina</v>
       </c>
       <c r="C39">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B39&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B39&amp;",", ", "&amp;Keys!$C$61&amp;",")), V39*T39/(T39+U39), T39)</f>
         <v>1720378</v>
       </c>
       <c r="D39">
@@ -17643,7 +18415,7 @@
         <v>14373</v>
       </c>
       <c r="E39">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B39&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B39&amp;",", ", "&amp;Keys!$C$61&amp;",")), V39*U39/(T39+U39), U39)</f>
         <v>3204874</v>
       </c>
       <c r="F39">
@@ -17702,8 +18474,27 @@
         <f t="shared" si="1"/>
         <v>125526</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T39">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B39&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1720378</v>
+      </c>
+      <c r="U39">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B39&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3204874</v>
+      </c>
+      <c r="V39">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B39, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>5114700</v>
+      </c>
+      <c r="W39" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B39&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <v>9733</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>132</v>
       </c>
@@ -17712,7 +18503,7 @@
         <v>South Dakota</v>
       </c>
       <c r="C40">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B40&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B40&amp;",", ", "&amp;Keys!$C$61&amp;",")), V40*T40/(T40+U40), T40)</f>
         <v>282489</v>
       </c>
       <c r="D40">
@@ -17720,7 +18511,7 @@
         <v>23104</v>
       </c>
       <c r="E40">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B40&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B40&amp;",", ", "&amp;Keys!$C$61&amp;",")), V40*U40/(T40+U40), U40)</f>
         <v>954076</v>
       </c>
       <c r="F40">
@@ -17779,8 +18570,27 @@
         <f t="shared" si="1"/>
         <v>147254</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T40">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B40&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>282489</v>
+      </c>
+      <c r="U40">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B40&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>954076</v>
+      </c>
+      <c r="V40">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B40, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>980000</v>
+      </c>
+      <c r="W40" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B40&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>134</v>
       </c>
@@ -17789,7 +18599,7 @@
         <v>Tennessee</v>
       </c>
       <c r="C41">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B41&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B41&amp;",", ", "&amp;Keys!$C$61&amp;",")), V41*T41/(T41+U41), T41)</f>
         <v>2253028</v>
       </c>
       <c r="D41">
@@ -17797,7 +18607,7 @@
         <v>21864</v>
       </c>
       <c r="E41">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B41&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B41&amp;",", ", "&amp;Keys!$C$61&amp;",")), V41*U41/(T41+U41), U41)</f>
         <v>4696396</v>
       </c>
       <c r="F41">
@@ -17856,8 +18666,27 @@
         <f t="shared" si="1"/>
         <v>204353</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T41">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B41&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2253028</v>
+      </c>
+      <c r="U41">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B41&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>4696396</v>
+      </c>
+      <c r="V41">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B41, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>6600400</v>
+      </c>
+      <c r="W41" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B41&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X41">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>136</v>
       </c>
@@ -17866,7 +18695,7 @@
         <v>Texas</v>
       </c>
       <c r="C42">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B42&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B42&amp;",", ", "&amp;Keys!$C$61&amp;",")), V42*T42/(T42+U42), T42)</f>
         <v>7281613</v>
       </c>
       <c r="D42">
@@ -17874,7 +18703,7 @@
         <v>65085</v>
       </c>
       <c r="E42">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B42&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B42&amp;",", ", "&amp;Keys!$C$61&amp;",")), V42*U42/(T42+U42), U42)</f>
         <v>15933517</v>
       </c>
       <c r="F42">
@@ -17933,8 +18762,27 @@
         <f t="shared" si="1"/>
         <v>326186</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T42">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B42&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>7281613</v>
+      </c>
+      <c r="U42">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B42&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>15933517</v>
+      </c>
+      <c r="V42">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B42, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>26155300</v>
+      </c>
+      <c r="W42" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B42&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X42">
+        <v>149654</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>138</v>
       </c>
@@ -17943,7 +18791,7 @@
         <v>Utah</v>
       </c>
       <c r="C43">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B43&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B43&amp;",", ", "&amp;Keys!$C$61&amp;",")), V43*T43/(T43+U43), T43)</f>
         <v>970972</v>
       </c>
       <c r="D43">
@@ -17951,7 +18799,7 @@
         <v>8026</v>
       </c>
       <c r="E43">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B43&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B43&amp;",", ", "&amp;Keys!$C$61&amp;",")), V43*U43/(T43+U43), U43)</f>
         <v>1971362</v>
       </c>
       <c r="F43">
@@ -18010,8 +18858,27 @@
         <f t="shared" si="1"/>
         <v>256780</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T43">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B43&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>970972</v>
+      </c>
+      <c r="U43">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B43&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1971362</v>
+      </c>
+      <c r="V43">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B43, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>3140100</v>
+      </c>
+      <c r="W43" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B43&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>140</v>
       </c>
@@ -18020,7 +18887,7 @@
         <v>Vermont</v>
       </c>
       <c r="C44">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B44&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B44&amp;",", ", "&amp;Keys!$C$61&amp;",")), V44*T44/(T44+U44), T44)</f>
         <v>164231</v>
       </c>
       <c r="D44">
@@ -18028,7 +18895,7 @@
         <v>2162</v>
       </c>
       <c r="E44">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B44&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B44&amp;",", ", "&amp;Keys!$C$61&amp;",")), V44*U44/(T44+U44), U44)</f>
         <v>473556</v>
       </c>
       <c r="F44">
@@ -18087,8 +18954,27 @@
         <f t="shared" si="1"/>
         <v>31427</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T44">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B44&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>164231</v>
+      </c>
+      <c r="U44">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B44&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>473556</v>
+      </c>
+      <c r="V44">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B44, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>587100</v>
+      </c>
+      <c r="W44" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B44&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>142</v>
       </c>
@@ -18097,7 +18983,7 @@
         <v>Virginia</v>
       </c>
       <c r="C45">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B45&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B45&amp;",", ", "&amp;Keys!$C$61&amp;",")), V45*T45/(T45+U45), T45)</f>
         <v>2833864</v>
       </c>
       <c r="D45">
@@ -18105,7 +18991,7 @@
         <v>36579</v>
       </c>
       <c r="E45">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B45&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B45&amp;",", ", "&amp;Keys!$C$61&amp;",")), V45*U45/(T45+U45), U45)</f>
         <v>4924472</v>
       </c>
       <c r="F45">
@@ -18164,8 +19050,27 @@
         <f t="shared" si="1"/>
         <v>190615</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T45">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B45&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2833864</v>
+      </c>
+      <c r="U45">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B45&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>4924472</v>
+      </c>
+      <c r="V45">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B45, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>7814000</v>
+      </c>
+      <c r="W45" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B45&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>144</v>
       </c>
@@ -18174,7 +19079,7 @@
         <v>Washington</v>
       </c>
       <c r="C46">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B46&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B46&amp;",", ", "&amp;Keys!$C$61&amp;",")), V46*T46/(T46+U46), T46)</f>
         <v>2535919</v>
       </c>
       <c r="D46">
@@ -18182,7 +19087,7 @@
         <v>24254</v>
       </c>
       <c r="E46">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B46&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B46&amp;",", ", "&amp;Keys!$C$61&amp;",")), V46*U46/(T46+U46), U46)</f>
         <v>4758579</v>
       </c>
       <c r="F46">
@@ -18241,8 +19146,27 @@
         <f t="shared" si="1"/>
         <v>200298</v>
       </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T46">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B46&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>2535919</v>
+      </c>
+      <c r="U46">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B46&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>4758579</v>
+      </c>
+      <c r="V46">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B46, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>6831300</v>
+      </c>
+      <c r="W46" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B46&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <v>71286</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>146</v>
       </c>
@@ -18251,7 +19175,7 @@
         <v>West Virginia</v>
       </c>
       <c r="C47">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B47&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B47&amp;",", ", "&amp;Keys!$C$61&amp;",")), V47*T47/(T47+U47), T47)</f>
         <v>398614</v>
       </c>
       <c r="D47">
@@ -18259,7 +19183,7 @@
         <v>160</v>
       </c>
       <c r="E47">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B47&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B47&amp;",", ", "&amp;Keys!$C$61&amp;",")), V47*U47/(T47+U47), U47)</f>
         <v>1032694</v>
       </c>
       <c r="F47">
@@ -18318,8 +19242,27 @@
         <f t="shared" si="1"/>
         <v>47662</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T47">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B47&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>398614</v>
+      </c>
+      <c r="U47">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B47&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1032694</v>
+      </c>
+      <c r="V47">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B47, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>1520900</v>
+      </c>
+      <c r="W47" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B47&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>148</v>
       </c>
@@ -18328,7 +19271,7 @@
         <v>Wisconsin</v>
       </c>
       <c r="C48">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B48&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B48&amp;",", ", "&amp;Keys!$C$61&amp;",")), V48*T48/(T48+U48), T48)</f>
         <v>1626951</v>
       </c>
       <c r="D48">
@@ -18336,7 +19279,7 @@
         <v>11536</v>
       </c>
       <c r="E48">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B48&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B48&amp;",", ", "&amp;Keys!$C$61&amp;",")), V48*U48/(T48+U48), U48)</f>
         <v>3918981</v>
       </c>
       <c r="F48">
@@ -18395,8 +19338,27 @@
         <f t="shared" si="1"/>
         <v>279308</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T48">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B48&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>1626951</v>
+      </c>
+      <c r="U48">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B48&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>3918981</v>
+      </c>
+      <c r="V48">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B48, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>5570100</v>
+      </c>
+      <c r="W48" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B48&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X48">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -18405,7 +19367,7 @@
         <v>Wyoming</v>
       </c>
       <c r="C49">
-        <f>INDEX(FHWA_MV1!D:D, MATCH(B49&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B49&amp;",", ", "&amp;Keys!$C$61&amp;",")), V49*T49/(T49+U49), T49)</f>
         <v>166107</v>
       </c>
       <c r="D49">
@@ -18413,7 +19375,7 @@
         <v>1953</v>
       </c>
       <c r="E49">
-        <f>INDEX(FHWA_MV1!J:J, MATCH(B49&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B49&amp;",", ", "&amp;Keys!$C$61&amp;",")), V49*U49/(T49+U49), U49)</f>
         <v>680479</v>
       </c>
       <c r="F49">
@@ -18472,15 +19434,34 @@
         <f t="shared" si="1"/>
         <v>28613</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T49">
+        <f>INDEX(FHWA_MV1!D:D, MATCH(B49&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>166107</v>
+      </c>
+      <c r="U49">
+        <f>INDEX(FHWA_MV1!J:J, MATCH(B49&amp;"*", FHWA_MV1!A:A, 0))</f>
+        <v>680479</v>
+      </c>
+      <c r="V49">
+        <f>IFERROR(SUM(INDEX(AFDC_state_fuel_2024!B:M, MATCH(B49, AFDC_state_fuel_2024!A:A, 0), 0)), 0)</f>
+        <v>666900</v>
+      </c>
+      <c r="W49" t="str">
+        <f>IF(ISNUMBER(SEARCH(", "&amp;B49&amp;",", ", "&amp;Keys!$C$61&amp;",")), "RE-ANCHORED to AFDC (see Keys / methodology 9.6)", "")</f>
+        <v/>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <f t="shared" ref="C50:S50" si="2">SUM(C2:C49)</f>
-        <v>96717875</v>
+        <f t="shared" ref="C50:V50" si="2">SUM(C2:C49)</f>
+        <v>93833515.428622678</v>
       </c>
       <c r="D50" s="4">
         <f t="shared" si="2"/>
@@ -18488,7 +19469,7 @@
       </c>
       <c r="E50" s="4">
         <f t="shared" si="2"/>
-        <v>188264643</v>
+        <v>181997685.57137734</v>
       </c>
       <c r="F50" s="4">
         <f t="shared" si="2"/>
@@ -18528,7 +19509,7 @@
       </c>
       <c r="O50" s="4">
         <f t="shared" si="2"/>
-        <v>269858277.90459502</v>
+        <v>261210416.9296234</v>
       </c>
       <c r="P50" s="4">
         <f t="shared" si="2"/>
@@ -18536,15 +19517,31 @@
       </c>
       <c r="Q50" s="4">
         <f t="shared" si="2"/>
-        <v>8158448.3044050001</v>
+        <v>7886869.7042356357</v>
       </c>
       <c r="R50" s="4">
         <f t="shared" si="2"/>
-        <v>6965791.7910000002</v>
+        <v>6733914.3661409607</v>
       </c>
       <c r="S50" s="4">
         <f t="shared" si="2"/>
         <v>9207532</v>
+      </c>
+      <c r="T50" s="4">
+        <f t="shared" si="2"/>
+        <v>96717875</v>
+      </c>
+      <c r="U50" s="4">
+        <f t="shared" si="2"/>
+        <v>188264643</v>
+      </c>
+      <c r="V50" s="4">
+        <f t="shared" si="2"/>
+        <v>287716900</v>
+      </c>
+      <c r="X50" s="4">
+        <f>SUM(X2:X49)</f>
+        <v>559233</v>
       </c>
     </row>
   </sheetData>
@@ -19024,10 +20021,10 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" ref="C15:I15" si="0">SUM(C2:C14)</f>
@@ -19065,7 +20062,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -19073,17 +20070,17 @@
     <col min="3" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>197</v>
@@ -19107,13 +20104,19 @@
         <v>215</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+        <v>378</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -19126,7 +20129,7 @@
         <v>17500</v>
       </c>
       <c r="D3">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B3=Keys!$C$62,C3*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L3)</f>
         <v>6800</v>
       </c>
       <c r="E3">
@@ -19157,8 +20160,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>187983.65774869543</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L3">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B3, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>6800</v>
+      </c>
+      <c r="M3" t="str">
+        <f>IF($B3=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -19171,7 +20182,7 @@
         <v>111200</v>
       </c>
       <c r="D4">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B4=Keys!$C$62,C4*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L4)</f>
         <v>29300</v>
       </c>
       <c r="E4">
@@ -19202,8 +20213,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>276482.42443226313</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L4">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B4, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>29300</v>
+      </c>
+      <c r="M4" t="str">
+        <f>IF($B4=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -19216,7 +20235,7 @@
         <v>9500</v>
       </c>
       <c r="D5">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B5=Keys!$C$62,C5*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L5)</f>
         <v>3800</v>
       </c>
       <c r="E5">
@@ -19247,8 +20266,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>131583.10424881158</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L5">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B5, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>3800</v>
+      </c>
+      <c r="M5" t="str">
+        <f>IF($B5=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -19261,7 +20288,7 @@
         <v>1533900</v>
       </c>
       <c r="D6">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B6=Keys!$C$62,C6*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L6)</f>
         <v>447100</v>
       </c>
       <c r="E6">
@@ -19292,8 +20319,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>955113.03054948407</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L6">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B6, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>447100</v>
+      </c>
+      <c r="M6" t="str">
+        <f>IF($B6=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -19306,7 +20341,7 @@
         <v>127000</v>
       </c>
       <c r="D7">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B7=Keys!$C$62,C7*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L7)</f>
         <v>48700</v>
       </c>
       <c r="E7">
@@ -19337,8 +20372,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>275557.67392458842</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L7">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B7, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>48700</v>
+      </c>
+      <c r="M7" t="str">
+        <f>IF($B7=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -19351,7 +20394,7 @@
         <v>39400</v>
       </c>
       <c r="D8">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B8=Keys!$C$62,C8*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L8)</f>
         <v>22500</v>
       </c>
       <c r="E8">
@@ -19382,8 +20425,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>52772.638619961275</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L8">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B8, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>22500</v>
+      </c>
+      <c r="M8" t="str">
+        <f>IF($B8=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -19396,7 +20447,7 @@
         <v>11100</v>
       </c>
       <c r="D9">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B9=Keys!$C$62,C9*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L9)</f>
         <v>4600</v>
       </c>
       <c r="E9">
@@ -19427,8 +20478,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>19507.861670187925</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L9">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B9, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>4600</v>
+      </c>
+      <c r="M9" t="str">
+        <f>IF($B9=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -19441,7 +20500,7 @@
         <v>334800</v>
       </c>
       <c r="D10">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B10=Keys!$C$62,C10*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L10)</f>
         <v>70400</v>
       </c>
       <c r="E10">
@@ -19472,8 +20531,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>543699.02644388902</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L10">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B10, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>70400</v>
+      </c>
+      <c r="M10" t="str">
+        <f>IF($B10=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>63</v>
       </c>
@@ -19486,7 +20553,7 @@
         <v>120000</v>
       </c>
       <c r="D11">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B11=Keys!$C$62,C11*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L11)</f>
         <v>26400</v>
       </c>
       <c r="E11">
@@ -19517,8 +20584,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>309828.56570259266</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L11">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B11, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>26400</v>
+      </c>
+      <c r="M11" t="str">
+        <f>IF($B11=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -19531,7 +20606,7 @@
         <v>11000</v>
       </c>
       <c r="D12">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B12=Keys!$C$62,C12*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L12)</f>
         <v>5600</v>
       </c>
       <c r="E12">
@@ -19562,8 +20637,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>195163.37170969215</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L12">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B12, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>5600</v>
+      </c>
+      <c r="M12" t="str">
+        <f>IF($B12=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -19576,7 +20659,7 @@
         <v>125500</v>
       </c>
       <c r="D13">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B13=Keys!$C$62,C13*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L13)</f>
         <v>40400</v>
       </c>
       <c r="E13">
@@ -19607,8 +20690,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>237013.48605396444</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L13">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B13, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>40400</v>
+      </c>
+      <c r="M13" t="str">
+        <f>IF($B13=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -19621,7 +20712,7 @@
         <v>34600</v>
       </c>
       <c r="D14">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B14=Keys!$C$62,C14*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L14)</f>
         <v>15300</v>
       </c>
       <c r="E14">
@@ -19652,8 +20743,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>217128.84653173512</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L14">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B14, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>15300</v>
+      </c>
+      <c r="M14" t="str">
+        <f>IF($B14=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -19666,7 +20765,7 @@
         <v>11700</v>
       </c>
       <c r="D15">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B15=Keys!$C$62,C15*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L15)</f>
         <v>7300</v>
       </c>
       <c r="E15">
@@ -19697,8 +20796,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>152647.79577873877</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L15">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B15, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>7300</v>
+      </c>
+      <c r="M15" t="str">
+        <f>IF($B15=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>76</v>
       </c>
@@ -19711,7 +20818,7 @@
         <v>14500</v>
       </c>
       <c r="D16">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B16=Keys!$C$62,C16*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L16)</f>
         <v>6600</v>
       </c>
       <c r="E16">
@@ -19742,8 +20849,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>118590.52941852008</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L16">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B16, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>6600</v>
+      </c>
+      <c r="M16" t="str">
+        <f>IF($B16=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -19756,7 +20871,7 @@
         <v>15000</v>
       </c>
       <c r="D17">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B17=Keys!$C$62,C17*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L17)</f>
         <v>6400</v>
       </c>
       <c r="E17">
@@ -19787,8 +20902,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>156673.57097551692</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L17">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B17, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>6400</v>
+      </c>
+      <c r="M17" t="str">
+        <f>IF($B17=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -19801,7 +20924,7 @@
         <v>11600</v>
       </c>
       <c r="D18">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B18=Keys!$C$62,C18*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L18)</f>
         <v>4600</v>
       </c>
       <c r="E18">
@@ -19832,8 +20955,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>184305.47356622454</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L18">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B18, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>4600</v>
+      </c>
+      <c r="M18" t="str">
+        <f>IF($B18=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -19846,7 +20977,7 @@
         <v>9700</v>
       </c>
       <c r="D19">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B19=Keys!$C$62,C19*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L19)</f>
         <v>9200</v>
       </c>
       <c r="E19">
@@ -19877,8 +21008,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>40377.429594660593</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L19">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B19, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>9200</v>
+      </c>
+      <c r="M19" t="str">
+        <f>IF($B19=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -19891,7 +21030,7 @@
         <v>94900</v>
       </c>
       <c r="D20">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B20=Keys!$C$62,C20*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L20)</f>
         <v>36600</v>
       </c>
       <c r="E20">
@@ -19922,8 +21061,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>119153.79939209727</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L20">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B20, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>36600</v>
+      </c>
+      <c r="M20" t="str">
+        <f>IF($B20=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -19936,7 +21083,7 @@
         <v>91100</v>
       </c>
       <c r="D21">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B21=Keys!$C$62,C21*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L21)</f>
         <v>52200</v>
       </c>
       <c r="E21">
@@ -19967,8 +21114,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>80043.921363822883</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L21">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B21, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>52200</v>
+      </c>
+      <c r="M21" t="str">
+        <f>IF($B21=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -19981,7 +21136,7 @@
         <v>75800</v>
       </c>
       <c r="D22">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B22=Keys!$C$62,C22*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L22)</f>
         <v>33600</v>
       </c>
       <c r="E22">
@@ -20012,8 +21167,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>251060.48068363895</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L22">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B22, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>33600</v>
+      </c>
+      <c r="M22" t="str">
+        <f>IF($B22=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>95</v>
       </c>
@@ -20026,7 +21189,7 @@
         <v>47400</v>
       </c>
       <c r="D23">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B23=Keys!$C$62,C23*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L23)</f>
         <v>20100</v>
       </c>
       <c r="E23">
@@ -20057,8 +21220,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>184371.78530762889</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L23">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B23, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>20100</v>
+      </c>
+      <c r="M23" t="str">
+        <f>IF($B23=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -20071,7 +21242,7 @@
         <v>4900</v>
       </c>
       <c r="D24">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B24=Keys!$C$62,C24*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L24)</f>
         <v>2400</v>
       </c>
       <c r="E24">
@@ -20102,8 +21273,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>113040.86013573325</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L24">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B24, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>2400</v>
+      </c>
+      <c r="M24" t="str">
+        <f>IF($B24=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>100</v>
       </c>
@@ -20116,7 +21295,7 @@
         <v>34200</v>
       </c>
       <c r="D25">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B25=Keys!$C$62,C25*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L25)</f>
         <v>16800</v>
       </c>
       <c r="E25">
@@ -20147,8 +21326,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>254541.74175239448</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L25">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B25, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>16800</v>
+      </c>
+      <c r="M25" t="str">
+        <f>IF($B25=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -20161,7 +21348,7 @@
         <v>5600</v>
       </c>
       <c r="D26">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B26=Keys!$C$62,C26*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L26)</f>
         <v>3200</v>
       </c>
       <c r="E26">
@@ -20192,8 +21379,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>111165.84887144259</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L26">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B26, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>3200</v>
+      </c>
+      <c r="M26" t="str">
+        <f>IF($B26=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -20206,7 +21401,7 @@
         <v>9100</v>
       </c>
       <c r="D27">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B27=Keys!$C$62,C27*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L27)</f>
         <v>4700</v>
       </c>
       <c r="E27">
@@ -20237,8 +21432,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>108669.57658396555</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L27">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B27, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>4700</v>
+      </c>
+      <c r="M27" t="str">
+        <f>IF($B27=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>106</v>
       </c>
@@ -20251,7 +21454,7 @@
         <v>65600</v>
       </c>
       <c r="D28">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B28=Keys!$C$62,C28*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L28)</f>
         <v>13400</v>
       </c>
       <c r="E28">
@@ -20282,8 +21485,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>116315.72693197224</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L28">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B28, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>13400</v>
+      </c>
+      <c r="M28" t="str">
+        <f>IF($B28=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>108</v>
       </c>
@@ -20296,7 +21507,7 @@
         <v>12700</v>
       </c>
       <c r="D29">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B29=Keys!$C$62,C29*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L29)</f>
         <v>8200</v>
       </c>
       <c r="E29">
@@ -20327,8 +21538,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>43793.622001170275</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L29">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B29, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>8200</v>
+      </c>
+      <c r="M29" t="str">
+        <f>IF($B29=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>110</v>
       </c>
@@ -20341,7 +21560,7 @@
         <v>173800</v>
       </c>
       <c r="D30">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B30=Keys!$C$62,C30*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L30)</f>
         <v>51600</v>
       </c>
       <c r="E30">
@@ -20372,8 +21591,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>112857.96569482631</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L30">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B30, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>51600</v>
+      </c>
+      <c r="M30" t="str">
+        <f>IF($B30=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -20386,7 +21613,7 @@
         <v>13000</v>
       </c>
       <c r="D31">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B31=Keys!$C$62,C31*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L31)</f>
         <v>5800</v>
       </c>
       <c r="E31">
@@ -20417,8 +21644,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>124615.42639302314</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L31">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B31, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>5800</v>
+      </c>
+      <c r="M31" t="str">
+        <f>IF($B31=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>114</v>
       </c>
@@ -20431,7 +21666,7 @@
         <v>168100</v>
       </c>
       <c r="D32">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B32=Keys!$C$62,C32*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L32)</f>
         <v>111400</v>
       </c>
       <c r="E32">
@@ -20462,8 +21697,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>208684.46526720689</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L32">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B32, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>111400</v>
+      </c>
+      <c r="M32" t="str">
+        <f>IF($B32=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>116</v>
       </c>
@@ -20476,7 +21719,7 @@
         <v>91000</v>
       </c>
       <c r="D33">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B33=Keys!$C$62,C33*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L33)</f>
         <v>28300</v>
       </c>
       <c r="E33">
@@ -20507,8 +21750,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>300014.68281776621</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L33">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B33, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>28300</v>
+      </c>
+      <c r="M33" t="str">
+        <f>IF($B33=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>118</v>
       </c>
@@ -20521,7 +21772,7 @@
         <v>1300</v>
       </c>
       <c r="D34">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B34=Keys!$C$62,C34*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L34)</f>
         <v>1000</v>
       </c>
       <c r="E34">
@@ -20552,8 +21803,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>67378.536462909498</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L34">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B34, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>1000</v>
+      </c>
+      <c r="M34" t="str">
+        <f>IF($B34=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>120</v>
       </c>
@@ -20566,7 +21825,7 @@
         <v>69400</v>
       </c>
       <c r="D35">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B35=Keys!$C$62,C35*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L35)</f>
         <v>29700</v>
       </c>
       <c r="E35">
@@ -20597,8 +21856,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>273402.90467388433</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L35">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B35, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>29700</v>
+      </c>
+      <c r="M35" t="str">
+        <f>IF($B35=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>122</v>
       </c>
@@ -20611,8 +21878,8 @@
         <v>22600</v>
       </c>
       <c r="D36">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
-        <v>34300</v>
+        <f>IF($B36=Keys!$C$62,C36*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L36)</f>
+        <v>7631.5207496058792</v>
       </c>
       <c r="E36">
         <f>IFERROR(INDEX(AFDC_state_fuel_2024!G:G, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
@@ -20642,8 +21909,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>214659.9569559645</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L36">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B36, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>34300</v>
+      </c>
+      <c r="M36" t="str">
+        <f>IF($B36=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v>OVERRIDDEN (see Keys / methodology 9.5)</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>124</v>
       </c>
@@ -20656,7 +21931,7 @@
         <v>78400</v>
       </c>
       <c r="D37">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B37=Keys!$C$62,C37*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L37)</f>
         <v>33200</v>
       </c>
       <c r="E37">
@@ -20687,8 +21962,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>279283.03380228241</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L37">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B37, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>33200</v>
+      </c>
+      <c r="M37" t="str">
+        <f>IF($B37=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>126</v>
       </c>
@@ -20701,7 +21984,7 @@
         <v>89900</v>
       </c>
       <c r="D38">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B38=Keys!$C$62,C38*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L38)</f>
         <v>47600</v>
       </c>
       <c r="E38">
@@ -20732,8 +22015,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>268657.8756034089</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L38">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B38, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>47600</v>
+      </c>
+      <c r="M38" t="str">
+        <f>IF($B38=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>128</v>
       </c>
@@ -20746,7 +22037,7 @@
         <v>8300</v>
       </c>
       <c r="D39">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B39=Keys!$C$62,C39*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L39)</f>
         <v>6000</v>
       </c>
       <c r="E39">
@@ -20777,8 +22068,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>14392.279713715829</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L39">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B39, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>6000</v>
+      </c>
+      <c r="M39" t="str">
+        <f>IF($B39=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>130</v>
       </c>
@@ -20791,7 +22090,7 @@
         <v>26800</v>
       </c>
       <c r="D40">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B40=Keys!$C$62,C40*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L40)</f>
         <v>11100</v>
       </c>
       <c r="E40">
@@ -20822,8 +22121,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>162121.1064962938</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L40">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B40, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>11100</v>
+      </c>
+      <c r="M40" t="str">
+        <f>IF($B40=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>132</v>
       </c>
@@ -20836,7 +22143,7 @@
         <v>2300</v>
       </c>
       <c r="D41">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B41=Keys!$C$62,C41*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L41)</f>
         <v>1700</v>
       </c>
       <c r="E41">
@@ -20867,8 +22174,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>80108.051948051943</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L41">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B41, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>1700</v>
+      </c>
+      <c r="M41" t="str">
+        <f>IF($B41=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>134</v>
       </c>
@@ -20881,7 +22196,7 @@
         <v>42600</v>
       </c>
       <c r="D42">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B42=Keys!$C$62,C42*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L42)</f>
         <v>12800</v>
       </c>
       <c r="E42">
@@ -20912,8 +22227,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>222024.65008373407</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L42">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B42, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>12800</v>
+      </c>
+      <c r="M42" t="str">
+        <f>IF($B42=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>136</v>
       </c>
@@ -20926,7 +22249,7 @@
         <v>294700</v>
       </c>
       <c r="D43">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B43=Keys!$C$62,C43*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L43)</f>
         <v>64700</v>
       </c>
       <c r="E43">
@@ -20957,8 +22280,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>1272943.2186952289</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L43">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B43, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>64700</v>
+      </c>
+      <c r="M43" t="str">
+        <f>IF($B43=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>138</v>
       </c>
@@ -20971,7 +22302,7 @@
         <v>52200</v>
       </c>
       <c r="D44">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B44=Keys!$C$62,C44*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L44)</f>
         <v>15500</v>
       </c>
       <c r="E44">
@@ -21002,8 +22333,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>238008.01576872537</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L44">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B44, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>15500</v>
+      </c>
+      <c r="M44" t="str">
+        <f>IF($B44=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>140</v>
       </c>
@@ -21016,7 +22355,7 @@
         <v>10200</v>
       </c>
       <c r="D45">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B45=Keys!$C$62,C45*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L45)</f>
         <v>6900</v>
       </c>
       <c r="E45">
@@ -21047,8 +22386,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>21888.161387365068</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L45">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B45, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>6900</v>
+      </c>
+      <c r="M45" t="str">
+        <f>IF($B45=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>142</v>
       </c>
@@ -21061,7 +22408,7 @@
         <v>107400</v>
       </c>
       <c r="D46">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B46=Keys!$C$62,C46*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L46)</f>
         <v>32100</v>
       </c>
       <c r="E46">
@@ -21092,8 +22439,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>201463.93637754902</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L46">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B46, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>32100</v>
+      </c>
+      <c r="M46" t="str">
+        <f>IF($B46=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>144</v>
       </c>
@@ -21106,7 +22461,7 @@
         <v>191400</v>
       </c>
       <c r="D47">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B47=Keys!$C$62,C47*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L47)</f>
         <v>48500</v>
       </c>
       <c r="E47">
@@ -21137,8 +22492,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>353565.61531059555</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L47">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B47, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>48500</v>
+      </c>
+      <c r="M47" t="str">
+        <f>IF($B47=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>146</v>
       </c>
@@ -21151,7 +22514,7 @@
         <v>3800</v>
       </c>
       <c r="D48">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B48=Keys!$C$62,C48*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L48)</f>
         <v>2200</v>
       </c>
       <c r="E48">
@@ -21182,8 +22545,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>65922.413562942194</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L48">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B48, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>2200</v>
+      </c>
+      <c r="M48" t="str">
+        <f>IF($B48=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>148</v>
       </c>
@@ -21196,7 +22567,7 @@
         <v>32300</v>
       </c>
       <c r="D49">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B49=Keys!$C$62,C49*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L49)</f>
         <v>15100</v>
       </c>
       <c r="E49">
@@ -21227,8 +22598,16 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>205679.53275959316</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L49">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B49, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>15100</v>
+      </c>
+      <c r="M49" t="str">
+        <f>IF($B49=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>150</v>
       </c>
@@ -21241,7 +22620,7 @@
         <v>1500</v>
       </c>
       <c r="D50">
-        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <f>IF($B50=Keys!$C$62,C50*(IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0))/(IFERROR(INDEX(AFDC_state_fuel_2024!B:B, MATCH(Keys!$C$63, AFDC_state_fuel_2024!A:A, 0)), 0)),L50)</f>
         <v>1000</v>
       </c>
       <c r="E50">
@@ -21272,18 +22651,26 @@
         <f>(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0)) + (IFERROR(INDEX(AFDC_state_fuel_2024!M:M, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0))*(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0))/((IFERROR(INDEX(AFDC_state_fuel_2024!K:K, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!D:D, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!F:F, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!J:J, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0))+(IFERROR(INDEX(AFDC_state_fuel_2024!L:L, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0) + IFERROR(INDEX(AFDC_state_fuel_2024!E:E, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0)))</f>
         <v>85972.767788535421</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L50">
+        <f>IFERROR(INDEX(AFDC_state_fuel_2024!C:C, MATCH(B50, AFDC_state_fuel_2024!A:A, 0)), 0)</f>
+        <v>1000</v>
+      </c>
+      <c r="M50" t="str">
+        <f>IF($B50=Keys!$C$62,"OVERRIDDEN (see Keys / methodology 9.5)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="C51" s="4">
-        <f t="shared" ref="C51:K51" si="0">SUM(C3:C50)</f>
+        <f t="shared" ref="C51:L51" si="0">SUM(C3:C50)</f>
         <v>4460300</v>
       </c>
       <c r="D51" s="4">
         <f t="shared" si="0"/>
-        <v>1506700</v>
+        <v>1480031.520749606</v>
       </c>
       <c r="E51" s="4">
         <f t="shared" si="0"/>
@@ -21312,6 +22699,10 @@
       <c r="K51" s="4">
         <f t="shared" si="0"/>
         <v>10210230.447556995</v>
+      </c>
+      <c r="L51" s="4">
+        <f t="shared" si="0"/>
+        <v>1506700</v>
       </c>
     </row>
   </sheetData>
@@ -21336,7 +22727,7 @@
         <v>117</v>
       </c>
       <c r="C1" s="8">
-        <v>46218</v>
+        <v>46245</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>36</v>
@@ -21806,36 +23197,36 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
@@ -21847,24 +23238,24 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H2">
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -21876,24 +23267,24 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="F3">
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H3">
         <v>8</v>
       </c>
       <c r="I3" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="B4" t="s">
         <v>45</v>
@@ -21905,24 +23296,24 @@
         <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H4">
         <v>7</v>
       </c>
       <c r="I4" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -21934,24 +23325,24 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H5">
         <v>9</v>
       </c>
       <c r="I5" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -21963,24 +23354,24 @@
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H6">
         <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -21992,24 +23383,24 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -22021,24 +23412,24 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H8">
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="B9" t="s">
         <v>60</v>
@@ -22050,24 +23441,24 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F9">
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H9">
         <v>5</v>
       </c>
       <c r="I9" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="B10" t="s">
         <v>63</v>
@@ -22079,24 +23470,24 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H10">
         <v>5</v>
       </c>
       <c r="I10" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="B11" t="s">
         <v>66</v>
@@ -22108,24 +23499,24 @@
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="F11">
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H11">
         <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="B12" t="s">
         <v>68</v>
@@ -22137,24 +23528,24 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H12">
         <v>3</v>
       </c>
       <c r="I12" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="B13" t="s">
         <v>71</v>
@@ -22166,24 +23557,24 @@
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H13">
         <v>3</v>
       </c>
       <c r="I13" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="B14" t="s">
         <v>74</v>
@@ -22195,24 +23586,24 @@
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H14">
         <v>4</v>
       </c>
       <c r="I14" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="B15" t="s">
         <v>76</v>
@@ -22224,24 +23615,24 @@
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H15">
         <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="B16" t="s">
         <v>79</v>
@@ -22253,24 +23644,24 @@
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
       <c r="G16" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H16">
         <v>6</v>
       </c>
       <c r="I16" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="B17" t="s">
         <v>82</v>
@@ -22282,24 +23673,24 @@
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H17">
         <v>7</v>
       </c>
       <c r="I17" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="B18" t="s">
         <v>84</v>
@@ -22311,24 +23702,24 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="B19" t="s">
         <v>87</v>
@@ -22340,24 +23731,24 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F19">
         <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H19">
         <v>5</v>
       </c>
       <c r="I19" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="B20" t="s">
         <v>90</v>
@@ -22369,24 +23760,24 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="B21" t="s">
         <v>92</v>
@@ -22398,24 +23789,24 @@
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H21">
         <v>3</v>
       </c>
       <c r="I21" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="B22" t="s">
         <v>95</v>
@@ -22427,24 +23818,24 @@
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F22">
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H22">
         <v>4</v>
       </c>
       <c r="I22" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="B23" t="s">
         <v>98</v>
@@ -22456,24 +23847,24 @@
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="F23">
         <v>3</v>
       </c>
       <c r="G23" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H23">
         <v>6</v>
       </c>
       <c r="I23" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="B24" t="s">
         <v>100</v>
@@ -22485,24 +23876,24 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F24">
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H24">
         <v>4</v>
       </c>
       <c r="I24" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="B25" t="s">
         <v>102</v>
@@ -22514,24 +23905,24 @@
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="F25">
         <v>4</v>
       </c>
       <c r="G25" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H25">
         <v>8</v>
       </c>
       <c r="I25" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="B26" t="s">
         <v>104</v>
@@ -22543,24 +23934,24 @@
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H26">
         <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="B27" t="s">
         <v>106</v>
@@ -22572,24 +23963,24 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="F27">
         <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H27">
         <v>8</v>
       </c>
       <c r="I27" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="B28" t="s">
         <v>108</v>
@@ -22601,24 +23992,24 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="B29" t="s">
         <v>110</v>
@@ -22630,24 +24021,24 @@
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H29">
         <v>2</v>
       </c>
       <c r="I29" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="B30" t="s">
         <v>112</v>
@@ -22659,24 +24050,24 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="F30">
         <v>4</v>
       </c>
       <c r="G30" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H30">
         <v>8</v>
       </c>
       <c r="I30" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="B31" t="s">
         <v>114</v>
@@ -22688,24 +24079,24 @@
         <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H31">
         <v>2</v>
       </c>
       <c r="I31" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="B32" t="s">
         <v>116</v>
@@ -22717,24 +24108,24 @@
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F32">
         <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H32">
         <v>5</v>
       </c>
       <c r="I32" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="B33" t="s">
         <v>118</v>
@@ -22746,24 +24137,24 @@
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F33">
         <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H33">
         <v>4</v>
       </c>
       <c r="I33" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="B34" t="s">
         <v>120</v>
@@ -22775,24 +24166,24 @@
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H34">
         <v>3</v>
       </c>
       <c r="I34" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="B35" t="s">
         <v>122</v>
@@ -22804,24 +24195,24 @@
         <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="F35">
         <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H35">
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="B36" t="s">
         <v>124</v>
@@ -22833,24 +24224,24 @@
         <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="F36">
         <v>4</v>
       </c>
       <c r="G36" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H36">
         <v>9</v>
       </c>
       <c r="I36" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="B37" t="s">
         <v>126</v>
@@ -22862,24 +24253,24 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H37">
         <v>2</v>
       </c>
       <c r="I37" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="B38" t="s">
         <v>128</v>
@@ -22891,24 +24282,24 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="B39" t="s">
         <v>130</v>
@@ -22920,24 +24311,24 @@
         <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F39">
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H39">
         <v>5</v>
       </c>
       <c r="I39" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="B40" t="s">
         <v>132</v>
@@ -22949,24 +24340,24 @@
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F40">
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H40">
         <v>4</v>
       </c>
       <c r="I40" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="B41" t="s">
         <v>134</v>
@@ -22978,24 +24369,24 @@
         <v>6</v>
       </c>
       <c r="E41" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="F41">
         <v>3</v>
       </c>
       <c r="G41" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H41">
         <v>6</v>
       </c>
       <c r="I41" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="B42" t="s">
         <v>136</v>
@@ -23007,24 +24398,24 @@
         <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="F42">
         <v>3</v>
       </c>
       <c r="G42" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H42">
         <v>7</v>
       </c>
       <c r="I42" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="B43" t="s">
         <v>138</v>
@@ -23036,24 +24427,24 @@
         <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="F43">
         <v>4</v>
       </c>
       <c r="G43" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H43">
         <v>8</v>
       </c>
       <c r="I43" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="B44" t="s">
         <v>140</v>
@@ -23065,24 +24456,24 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="B45" t="s">
         <v>142</v>
@@ -23094,24 +24485,24 @@
         <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F45">
         <v>3</v>
       </c>
       <c r="G45" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H45">
         <v>5</v>
       </c>
       <c r="I45" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="B46" t="s">
         <v>144</v>
@@ -23123,24 +24514,24 @@
         <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="F46">
         <v>4</v>
       </c>
       <c r="G46" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H46">
         <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="B47" t="s">
         <v>146</v>
@@ -23152,24 +24543,24 @@
         <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F47">
         <v>3</v>
       </c>
       <c r="G47" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H47">
         <v>5</v>
       </c>
       <c r="I47" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="B48" t="s">
         <v>148</v>
@@ -23181,24 +24572,24 @@
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="F48">
         <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H48">
         <v>3</v>
       </c>
       <c r="I48" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="B49" t="s">
         <v>150</v>
@@ -23210,19 +24601,19 @@
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="F49">
         <v>4</v>
       </c>
       <c r="G49" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H49">
         <v>8</v>
       </c>
       <c r="I49" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -23238,129 +24629,129 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="P3" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="E5" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="H5" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="K5" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="N5" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="B6" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="C7" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="E7" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="F7" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="H7" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="I7" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="K7" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="L7" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="N7" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="O7" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="C8" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="D8" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="E8" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="F8" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="G8" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="H8" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="I8" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="J8" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="K8" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="L8" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="M8" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="N8" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="O8" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="P8" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="B10">
         <v>1932886</v>
@@ -23410,7 +24801,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="B11">
         <v>120421</v>
@@ -23510,7 +24901,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="B13">
         <v>892704</v>
@@ -23560,7 +24951,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="B14">
         <v>12737763</v>
@@ -23610,7 +25001,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="B15">
         <v>1341494</v>
@@ -23660,7 +25051,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="B16">
         <v>1028325</v>
@@ -23710,7 +25101,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="B17">
         <v>146701</v>
@@ -23760,7 +25151,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="B18">
         <v>138559</v>
@@ -23810,7 +25201,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="B19">
         <v>7113843</v>
@@ -23860,7 +25251,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="B20">
         <v>3154970</v>
@@ -23910,7 +25301,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="B21">
         <v>415330</v>
@@ -24010,7 +25401,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="B23">
         <v>3443638</v>
@@ -24060,7 +25451,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="B24">
         <v>1752726</v>
@@ -24110,7 +25501,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="B25">
         <v>998101</v>
@@ -24310,7 +25701,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="B29">
         <v>305020</v>
@@ -24410,7 +25801,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="B31">
         <v>1690199</v>
@@ -24460,7 +25851,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="B32">
         <v>2493266</v>
@@ -24510,7 +25901,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="B33">
         <v>1592071</v>
@@ -24560,7 +25951,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B34">
         <v>754721</v>
@@ -24610,7 +26001,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="B35">
         <v>1644583</v>
@@ -24660,7 +26051,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="B36">
         <v>524624</v>
@@ -24760,7 +26151,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="B38">
         <v>832098</v>
@@ -24860,7 +26251,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="B40">
         <v>2251730</v>
@@ -24960,7 +26351,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="B42">
         <v>6452828</v>
@@ -25210,7 +26601,7 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="B47">
         <v>1291044</v>
@@ -25310,7 +26701,7 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="B49">
         <v>304190</v>
@@ -25410,7 +26801,7 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="B51">
         <v>275993</v>
@@ -25460,7 +26851,7 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="B52">
         <v>2211560</v>
@@ -25510,7 +26901,7 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="B53">
         <v>7184055</v>
@@ -25710,7 +27101,7 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="B57">
         <v>2476547</v>
@@ -25760,7 +27151,7 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="B58">
         <v>391085</v>
@@ -25810,7 +27201,7 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="B59">
         <v>1594530</v>
@@ -25860,7 +27251,7 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="B60">
         <v>157686</v>
@@ -25910,7 +27301,7 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B61">
         <v>96058245</v>
@@ -25960,17 +27351,17 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -25985,7 +27376,7 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.45">
@@ -25993,7 +27384,7 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.45">
@@ -26006,7 +27397,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="C5">
         <v>2697</v>
@@ -26062,7 +27453,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="C12">
         <v>8066</v>
@@ -26086,7 +27477,7 @@
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="C15">
         <v>25565</v>
@@ -26416,17 +27807,17 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
@@ -26434,40 +27825,40 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="C5" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="D5" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="E5" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="F5" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="G5" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="H5" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="I5" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="J5" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="K5" t="s">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="L5" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="M5" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.45">
@@ -26513,7 +27904,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="B7">
         <v>3400</v>
@@ -26800,7 +28191,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="B14">
         <v>10100</v>
@@ -26923,7 +28314,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="B17">
         <v>29900</v>
@@ -28563,7 +29954,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>504</v>
+        <v>332</v>
       </c>
       <c r="B57">
         <v>4503700</v>
@@ -28614,36 +30005,36 @@
   <sheetData>
     <row r="1" spans="1:53" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:53" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="I3" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="N3" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="P3" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="W3" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="AD3" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="AQ3" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="AU3" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="AY3" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
     </row>
     <row r="4" spans="1:53" x14ac:dyDescent="0.45">
@@ -28654,19 +30045,19 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="D4" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="E4" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="F4" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="G4" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="I4" t="s">
         <v>36</v>
@@ -28675,10 +30066,10 @@
         <v>36</v>
       </c>
       <c r="K4" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="L4" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="N4" t="s">
         <v>36</v>
@@ -28687,82 +30078,82 @@
         <v>36</v>
       </c>
       <c r="P4" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="Q4" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="R4" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="S4" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="T4" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="U4" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="V4" t="s">
         <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="X4" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="Y4" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="Z4" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="AA4" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="AB4" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="AC4" t="s">
         <v>45</v>
       </c>
       <c r="AD4" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="AE4" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="AF4" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="AG4" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="AH4" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="AI4" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="AL4" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="AM4" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="AN4" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="AO4" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="AQ4" t="s">
         <v>36</v>
@@ -28771,7 +30162,7 @@
         <v>36</v>
       </c>
       <c r="AS4" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="AU4" t="s">
         <v>36</v>
@@ -28780,7 +30171,7 @@
         <v>36</v>
       </c>
       <c r="AW4" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="AY4" t="s">
         <v>36</v>
@@ -28789,7 +30180,7 @@
         <v>36</v>
       </c>
       <c r="BA4" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5" spans="1:53" x14ac:dyDescent="0.45">
@@ -28940,10 +30331,10 @@
     </row>
     <row r="6" spans="1:53" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="B6" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="C6">
         <v>1.644587564340822E-3</v>
@@ -28961,10 +30352,10 @@
         <v>2.8763113095518602E-3</v>
       </c>
       <c r="I6" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="J6" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="K6">
         <v>5.7149773803734883E-3</v>
@@ -28973,10 +30364,10 @@
         <v>0.10138057301022239</v>
       </c>
       <c r="N6" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="O6" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -29057,28 +30448,28 @@
         <v>0</v>
       </c>
       <c r="AQ6" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="AR6" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="AS6">
         <v>0</v>
       </c>
       <c r="AU6" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="AV6" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="AW6">
         <v>4.4450299557348043E-3</v>
       </c>
       <c r="AY6" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="AZ6" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="BA6">
         <v>1.1597818782036759E-2</v>
@@ -30254,10 +31645,10 @@
     </row>
     <row r="15" spans="1:53" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="B15" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="C15">
         <v>4.5969813900990086E-3</v>
@@ -30275,10 +31666,10 @@
         <v>4.6018136938534024E-3</v>
       </c>
       <c r="I15" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="J15" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="K15">
         <v>1.9313574658021759E-2</v>
@@ -30287,10 +31678,10 @@
         <v>2.105747115191876E-2</v>
       </c>
       <c r="N15" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="O15" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -30371,28 +31762,28 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="AR15" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="AS15">
         <v>0</v>
       </c>
       <c r="AU15" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="AV15" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="AW15">
         <v>1.1499036419574779E-3</v>
       </c>
       <c r="AY15" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="AZ15" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="BA15">
         <v>5.6626216110088117E-3</v>
@@ -36133,7 +37524,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="B1" t="s">
         <v>198</v>
@@ -36325,7 +37716,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="B1" t="s">
         <v>198</v>
@@ -36521,7 +37912,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>198</v>
@@ -36759,7 +38150,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>198</v>
@@ -37081,7 +38472,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -37913,6 +39304,62 @@
       </c>
       <c r="D59" t="s">
         <v>321</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>317</v>
+      </c>
+      <c r="B60" t="s">
+        <v>322</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>324</v>
+      </c>
+      <c r="B61" t="s">
+        <v>325</v>
+      </c>
+      <c r="C61" t="s">
+        <v>326</v>
+      </c>
+      <c r="D61" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>328</v>
+      </c>
+      <c r="B62" t="s">
+        <v>329</v>
+      </c>
+      <c r="C62" t="s">
+        <v>121</v>
+      </c>
+      <c r="D62" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>328</v>
+      </c>
+      <c r="B63" t="s">
+        <v>331</v>
+      </c>
+      <c r="C63" t="s">
+        <v>332</v>
+      </c>
+      <c r="D63" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -37931,7 +39378,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -38179,7 +39626,7 @@
       </c>
       <c r="D9">
         <f>ROUND(MAX(0, State_lookup!O8 - B9-C9-E9-F9-G9-H9), 0)</f>
-        <v>378525</v>
+        <v>853623</v>
       </c>
       <c r="E9">
         <f>ROUND(AFDC_state_fuels_lookup!G9, 0)</f>
@@ -38757,7 +40204,7 @@
       </c>
       <c r="D26">
         <f>ROUND(MAX(0, State_lookup!O25 - B26-C26-E26-F26-G26-H26), 0)</f>
-        <v>1873929</v>
+        <v>951152</v>
       </c>
       <c r="E26">
         <f>ROUND(AFDC_state_fuels_lookup!G26, 0)</f>
@@ -38961,7 +40408,7 @@
       </c>
       <c r="D32">
         <f>ROUND(MAX(0, State_lookup!O31 - B32-C32-E32-F32-G32-H32), 0)</f>
-        <v>18602405</v>
+        <v>10402224</v>
       </c>
       <c r="E32">
         <f>ROUND(AFDC_state_fuels_lookup!G32, 0)</f>
@@ -39097,7 +40544,7 @@
       </c>
       <c r="D36">
         <f>ROUND(MAX(0, State_lookup!O35 - B36-C36-E36-F36-G36-H36), 0)</f>
-        <v>3273573</v>
+        <v>3300241</v>
       </c>
       <c r="E36">
         <f>ROUND(AFDC_state_fuels_lookup!G36, 0)</f>
@@ -39105,7 +40552,7 @@
       </c>
       <c r="F36">
         <f>ROUND(AFDC_state_fuels_lookup!D36, 0)</f>
-        <v>34300</v>
+        <v>7632</v>
       </c>
       <c r="G36">
         <f>ROUND(AFDC_state_fuels_lookup!H36, 0)</f>
@@ -39594,7 +41041,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
@@ -39606,7 +41053,7 @@
       </c>
       <c r="D51" s="4">
         <f t="shared" si="0"/>
-        <v>262291987</v>
+        <v>253670795</v>
       </c>
       <c r="E51" s="4">
         <f t="shared" si="0"/>
@@ -39614,7 +41061,7 @@
       </c>
       <c r="F51" s="4">
         <f t="shared" si="0"/>
-        <v>1506700</v>
+        <v>1480032</v>
       </c>
       <c r="G51" s="4">
         <f t="shared" si="0"/>
@@ -39627,7 +41074,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$2</f>
@@ -39660,7 +41107,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
@@ -39672,7 +41119,7 @@
       </c>
       <c r="D53" s="7">
         <f t="shared" si="1"/>
-        <v>1.8017338207137058E-2</v>
+        <v>-1.5443550295006412E-2</v>
       </c>
       <c r="E53" s="7">
         <f t="shared" si="1"/>
@@ -39680,7 +41127,7 @@
       </c>
       <c r="F53" s="7">
         <f t="shared" si="1"/>
-        <v>6.2684040696136686E-2</v>
+        <v>4.3874949306155556E-2</v>
       </c>
       <c r="G53" s="7">
         <f t="shared" si="1"/>
@@ -39707,7 +41154,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -41370,7 +42817,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
@@ -41403,7 +42850,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$3</f>
@@ -41436,7 +42883,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
@@ -41483,7 +42930,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -43146,7 +44593,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
@@ -43179,7 +44626,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$4</f>
@@ -43212,7 +44659,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
@@ -43259,7 +44706,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -44922,7 +46369,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
@@ -44955,7 +46402,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$5</f>
@@ -44988,7 +46435,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
@@ -45035,7 +46482,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -46698,7 +48145,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" ref="B51:H51" si="0">SUM(B3:B50)</f>
@@ -46731,7 +48178,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B52" s="4">
         <f>National_totals!$C$6</f>
@@ -46764,7 +48211,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7">
         <f t="shared" ref="B53:H53" si="1">IFERROR((B51-B52)/B52, 0)</f>
